--- a/research/traditional_assets/database/data/belgium/belgium_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_furn_home_furnishings.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09374152232619365</v>
+        <v>0.09354091852037816</v>
       </c>
       <c r="C2">
-        <v>183.1079552278404</v>
+        <v>181.3714213245331</v>
       </c>
       <c r="D2">
-        <v>152.0079552278404</v>
+        <v>152.2224213245331</v>
       </c>
       <c r="E2">
-        <v>-171.3</v>
+        <v>-169.349</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.951</v>
       </c>
       <c r="G2">
         <v>31.1</v>
@@ -1445,28 +1445,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09813530000000001</v>
       </c>
       <c r="N2">
-        <v>40.53333333333333</v>
+        <v>40.43519803333333</v>
       </c>
       <c r="O2">
-        <v>10.13333333333333</v>
+        <v>10.10879950833333</v>
       </c>
       <c r="P2">
-        <v>30.4</v>
+        <v>30.32639852499999</v>
       </c>
       <c r="Q2">
-        <v>51.7</v>
+        <v>51.626398525</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09374152232619365</v>
+        <v>0.09410471567714966</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460945</v>
+        <v>0.9415488180676558</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>413.0352007211811</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09354091852037816</v>
+        <v>0.09334031471456268</v>
       </c>
       <c r="C3">
-        <v>181.3714213245331</v>
+        <v>179.6354934512589</v>
       </c>
       <c r="D3">
-        <v>152.2224213245331</v>
+        <v>152.4374934512589</v>
       </c>
       <c r="E3">
-        <v>-169.349</v>
+        <v>-167.398</v>
       </c>
       <c r="F3">
-        <v>1.951</v>
+        <v>3.902000000000001</v>
       </c>
       <c r="G3">
         <v>31.1</v>
@@ -1527,28 +1527,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M3">
-        <v>0.09813530000000001</v>
+        <v>0.1962706</v>
       </c>
       <c r="N3">
-        <v>40.43519803333333</v>
+        <v>40.33706273333333</v>
       </c>
       <c r="O3">
-        <v>10.10879950833333</v>
+        <v>10.08426568333333</v>
       </c>
       <c r="P3">
-        <v>30.32639852499999</v>
+        <v>30.25279705</v>
       </c>
       <c r="Q3">
-        <v>51.626398525</v>
+        <v>51.55279705</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09410471567714966</v>
+        <v>0.09447532113730886</v>
       </c>
       <c r="T3">
-        <v>0.9415488180676558</v>
+        <v>0.9487726082937389</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>413.0352007211811</v>
+        <v>206.5176003605906</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09334031471456268</v>
+        <v>0.09313971090874719</v>
       </c>
       <c r="C4">
-        <v>179.6354934512589</v>
+        <v>177.9001741803969</v>
       </c>
       <c r="D4">
-        <v>152.4374934512589</v>
+        <v>152.6531741803969</v>
       </c>
       <c r="E4">
-        <v>-167.398</v>
+        <v>-165.447</v>
       </c>
       <c r="F4">
-        <v>3.902000000000001</v>
+        <v>5.853000000000001</v>
       </c>
       <c r="G4">
         <v>31.1</v>
@@ -1609,28 +1609,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M4">
-        <v>0.1962706</v>
+        <v>0.2944059</v>
       </c>
       <c r="N4">
-        <v>40.33706273333333</v>
+        <v>40.23892743333333</v>
       </c>
       <c r="O4">
-        <v>10.08426568333333</v>
+        <v>10.05973185833333</v>
       </c>
       <c r="P4">
-        <v>30.25279705</v>
+        <v>30.179195575</v>
       </c>
       <c r="Q4">
-        <v>51.55279705</v>
+        <v>51.479195575</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09447532113730886</v>
+        <v>0.09485356794716206</v>
       </c>
       <c r="T4">
-        <v>0.9487726082937389</v>
+        <v>0.9561453426481945</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>206.5176003605906</v>
+        <v>137.6784002403937</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09313971090874719</v>
+        <v>0.09293910710293171</v>
       </c>
       <c r="C5">
-        <v>177.9001741803969</v>
+        <v>176.1654660989051</v>
       </c>
       <c r="D5">
-        <v>152.6531741803969</v>
+        <v>152.8694660989051</v>
       </c>
       <c r="E5">
-        <v>-165.447</v>
+        <v>-163.496</v>
       </c>
       <c r="F5">
-        <v>5.853000000000001</v>
+        <v>7.804000000000001</v>
       </c>
       <c r="G5">
         <v>31.1</v>
@@ -1691,28 +1691,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M5">
-        <v>0.2944059</v>
+        <v>0.3925412</v>
       </c>
       <c r="N5">
-        <v>40.23892743333333</v>
+        <v>40.14079213333333</v>
       </c>
       <c r="O5">
-        <v>10.05973185833333</v>
+        <v>10.03519803333333</v>
       </c>
       <c r="P5">
-        <v>30.179195575</v>
+        <v>30.1055941</v>
       </c>
       <c r="Q5">
-        <v>51.479195575</v>
+        <v>51.4055941</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09485356794716206</v>
+        <v>0.0952396948988872</v>
       </c>
       <c r="T5">
-        <v>0.9561453426481945</v>
+        <v>0.963671675635035</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>137.6784002403937</v>
+        <v>103.2588001802953</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09293910710293171</v>
+        <v>0.09273850329711623</v>
       </c>
       <c r="C6">
-        <v>176.1654660989051</v>
+        <v>174.4313718084239</v>
       </c>
       <c r="D6">
-        <v>152.8694660989051</v>
+        <v>153.0863718084239</v>
       </c>
       <c r="E6">
-        <v>-163.496</v>
+        <v>-161.545</v>
       </c>
       <c r="F6">
-        <v>7.804000000000001</v>
+        <v>9.755000000000003</v>
       </c>
       <c r="G6">
         <v>31.1</v>
@@ -1773,28 +1773,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M6">
-        <v>0.3925412</v>
+        <v>0.4906765000000001</v>
       </c>
       <c r="N6">
-        <v>40.14079213333333</v>
+        <v>40.04265683333333</v>
       </c>
       <c r="O6">
-        <v>10.03519803333333</v>
+        <v>10.01066420833333</v>
       </c>
       <c r="P6">
-        <v>30.1055941</v>
+        <v>30.031992625</v>
       </c>
       <c r="Q6">
-        <v>51.4055941</v>
+        <v>51.331992625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0952396948988872</v>
+        <v>0.09563395083906971</v>
       </c>
       <c r="T6">
-        <v>0.963671675635035</v>
+        <v>0.9713564577373877</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>103.2588001802953</v>
+        <v>82.60704014423622</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09273850329711623</v>
+        <v>0.09253789949130074</v>
       </c>
       <c r="C7">
-        <v>174.4313718084239</v>
+        <v>172.6978939253807</v>
       </c>
       <c r="D7">
-        <v>153.0863718084239</v>
+        <v>153.3038939253807</v>
       </c>
       <c r="E7">
-        <v>-161.545</v>
+        <v>-159.594</v>
       </c>
       <c r="F7">
-        <v>9.755000000000003</v>
+        <v>11.706</v>
       </c>
       <c r="G7">
         <v>31.1</v>
@@ -1855,28 +1855,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M7">
-        <v>0.4906765000000001</v>
+        <v>0.5888118000000001</v>
       </c>
       <c r="N7">
-        <v>40.04265683333333</v>
+        <v>39.94452153333333</v>
       </c>
       <c r="O7">
-        <v>10.01066420833333</v>
+        <v>9.986130383333332</v>
       </c>
       <c r="P7">
-        <v>30.031992625</v>
+        <v>29.95839115</v>
       </c>
       <c r="Q7">
-        <v>51.331992625</v>
+        <v>51.25839114999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09563395083906971</v>
+        <v>0.09603659520351143</v>
       </c>
       <c r="T7">
-        <v>0.9713564577373877</v>
+        <v>0.9792047458419182</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>82.60704014423622</v>
+        <v>68.83920012019685</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09253789949130074</v>
+        <v>0.09233729568548527</v>
       </c>
       <c r="C8">
-        <v>172.6978939253807</v>
+        <v>170.9650350810947</v>
       </c>
       <c r="D8">
-        <v>153.3038939253807</v>
+        <v>153.5220350810947</v>
       </c>
       <c r="E8">
-        <v>-159.594</v>
+        <v>-157.643</v>
       </c>
       <c r="F8">
-        <v>11.706</v>
+        <v>13.657</v>
       </c>
       <c r="G8">
         <v>31.1</v>
@@ -1937,28 +1937,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M8">
-        <v>0.5888118</v>
+        <v>0.6869470999999999</v>
       </c>
       <c r="N8">
-        <v>39.94452153333333</v>
+        <v>39.84638623333333</v>
       </c>
       <c r="O8">
-        <v>9.986130383333332</v>
+        <v>9.961596558333333</v>
       </c>
       <c r="P8">
-        <v>29.95839115</v>
+        <v>29.884789675</v>
       </c>
       <c r="Q8">
-        <v>51.25839114999999</v>
+        <v>51.184789675</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09603659520351143</v>
+        <v>0.09644789858654329</v>
       </c>
       <c r="T8">
-        <v>0.9792047458419182</v>
+        <v>0.9872218143357934</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>68.83920012019686</v>
+        <v>59.00502867445446</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09233729568548525</v>
+        <v>0.09213669187966977</v>
       </c>
       <c r="C9">
-        <v>170.9650350810947</v>
+        <v>169.2327979218833</v>
       </c>
       <c r="D9">
-        <v>153.5220350810947</v>
+        <v>153.7407979218833</v>
       </c>
       <c r="E9">
-        <v>-157.643</v>
+        <v>-155.692</v>
       </c>
       <c r="F9">
-        <v>13.657</v>
+        <v>15.608</v>
       </c>
       <c r="G9">
         <v>31.1</v>
@@ -2019,28 +2019,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M9">
-        <v>0.6869471000000001</v>
+        <v>0.7850824000000001</v>
       </c>
       <c r="N9">
-        <v>39.84638623333333</v>
+        <v>39.74825093333333</v>
       </c>
       <c r="O9">
-        <v>9.961596558333333</v>
+        <v>9.937062733333333</v>
       </c>
       <c r="P9">
-        <v>29.884789675</v>
+        <v>29.8111882</v>
       </c>
       <c r="Q9">
-        <v>51.184789675</v>
+        <v>51.1111882</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09644789858654329</v>
+        <v>0.09686814334746716</v>
       </c>
       <c r="T9">
-        <v>0.9872218143357934</v>
+        <v>0.9954131669273616</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>59.00502867445444</v>
+        <v>51.62940009014764</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09213669187966977</v>
+        <v>0.0919360880738543</v>
       </c>
       <c r="C10">
-        <v>169.2327979218833</v>
+        <v>167.501185109169</v>
       </c>
       <c r="D10">
-        <v>153.7407979218833</v>
+        <v>153.960185109169</v>
       </c>
       <c r="E10">
-        <v>-155.692</v>
+        <v>-153.741</v>
       </c>
       <c r="F10">
-        <v>15.608</v>
+        <v>17.559</v>
       </c>
       <c r="G10">
         <v>31.1</v>
@@ -2101,28 +2101,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M10">
-        <v>0.7850824000000001</v>
+        <v>0.8832177</v>
       </c>
       <c r="N10">
-        <v>39.74825093333333</v>
+        <v>39.65011563333333</v>
       </c>
       <c r="O10">
-        <v>9.937062733333333</v>
+        <v>9.912528908333332</v>
       </c>
       <c r="P10">
-        <v>29.8111882</v>
+        <v>29.737586725</v>
       </c>
       <c r="Q10">
-        <v>51.1111882</v>
+        <v>51.037586725</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09686814334746716</v>
+        <v>0.09729762425698274</v>
       </c>
       <c r="T10">
-        <v>0.9954131669273616</v>
+        <v>1.003784549246217</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>51.62940009014764</v>
+        <v>45.89280008013124</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0919360880738543</v>
+        <v>0.09173548426803882</v>
       </c>
       <c r="C11">
-        <v>167.501185109169</v>
+        <v>165.7701993195874</v>
       </c>
       <c r="D11">
-        <v>153.960185109169</v>
+        <v>154.1801993195874</v>
       </c>
       <c r="E11">
-        <v>-153.741</v>
+        <v>-151.79</v>
       </c>
       <c r="F11">
-        <v>17.559</v>
+        <v>19.51</v>
       </c>
       <c r="G11">
         <v>31.1</v>
@@ -2183,28 +2183,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M11">
-        <v>0.8832177</v>
+        <v>0.981353</v>
       </c>
       <c r="N11">
-        <v>39.65011563333333</v>
+        <v>39.55198033333333</v>
       </c>
       <c r="O11">
-        <v>9.912528908333332</v>
+        <v>9.887995083333333</v>
       </c>
       <c r="P11">
-        <v>29.737586725</v>
+        <v>29.66398525</v>
       </c>
       <c r="Q11">
-        <v>51.037586725</v>
+        <v>50.96398525</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09729762425698274</v>
+        <v>0.0977366491867098</v>
       </c>
       <c r="T11">
-        <v>1.003784549246217</v>
+        <v>1.012341962283269</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>45.89280008013124</v>
+        <v>41.30352007211812</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09173548426803882</v>
+        <v>0.09153488046222333</v>
       </c>
       <c r="C12">
-        <v>165.7701993195874</v>
+        <v>164.0398432450959</v>
       </c>
       <c r="D12">
-        <v>154.1801993195874</v>
+        <v>154.4008432450959</v>
       </c>
       <c r="E12">
-        <v>-151.79</v>
+        <v>-149.839</v>
       </c>
       <c r="F12">
-        <v>19.51000000000001</v>
+        <v>21.461</v>
       </c>
       <c r="G12">
         <v>31.1</v>
@@ -2265,28 +2265,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M12">
-        <v>0.9813530000000003</v>
+        <v>1.0794883</v>
       </c>
       <c r="N12">
-        <v>39.55198033333333</v>
+        <v>39.45384503333333</v>
       </c>
       <c r="O12">
-        <v>9.887995083333333</v>
+        <v>9.863461258333333</v>
       </c>
       <c r="P12">
-        <v>29.66398525</v>
+        <v>29.590383775</v>
       </c>
       <c r="Q12">
-        <v>50.96398525</v>
+        <v>50.890383775</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0977366491867098</v>
+        <v>0.09818553984519476</v>
       </c>
       <c r="T12">
-        <v>1.012341962283269</v>
+        <v>1.021091676736884</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>41.30352007211811</v>
+        <v>37.54865461101647</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09153488046222333</v>
+        <v>0.09133427665640785</v>
       </c>
       <c r="C13">
-        <v>164.0398432450959</v>
+        <v>162.3101195930837</v>
       </c>
       <c r="D13">
-        <v>154.4008432450959</v>
+        <v>154.6221195930837</v>
       </c>
       <c r="E13">
-        <v>-149.839</v>
+        <v>-147.888</v>
       </c>
       <c r="F13">
-        <v>21.461</v>
+        <v>23.412</v>
       </c>
       <c r="G13">
         <v>31.1</v>
@@ -2347,28 +2347,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M13">
-        <v>1.0794883</v>
+        <v>1.1776236</v>
       </c>
       <c r="N13">
-        <v>39.45384503333333</v>
+        <v>39.35570973333333</v>
       </c>
       <c r="O13">
-        <v>9.863461258333333</v>
+        <v>9.838927433333334</v>
       </c>
       <c r="P13">
-        <v>29.590383775</v>
+        <v>29.5167823</v>
       </c>
       <c r="Q13">
-        <v>50.890383775</v>
+        <v>50.8167823</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09818553984519476</v>
+        <v>0.09864463256409983</v>
       </c>
       <c r="T13">
-        <v>1.021091676736884</v>
+        <v>1.030040248337172</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>37.54865461101647</v>
+        <v>34.41960006009843</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09133427665640785</v>
+        <v>0.09113367285059235</v>
       </c>
       <c r="C14">
-        <v>162.3101195930837</v>
+        <v>160.5810310864823</v>
       </c>
       <c r="D14">
-        <v>154.6221195930837</v>
+        <v>154.8440310864823</v>
       </c>
       <c r="E14">
-        <v>-147.888</v>
+        <v>-145.937</v>
       </c>
       <c r="F14">
-        <v>23.412</v>
+        <v>25.363</v>
       </c>
       <c r="G14">
         <v>31.1</v>
@@ -2429,28 +2429,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M14">
-        <v>1.1776236</v>
+        <v>1.2757589</v>
       </c>
       <c r="N14">
-        <v>39.35570973333333</v>
+        <v>39.25757443333333</v>
       </c>
       <c r="O14">
-        <v>9.838927433333334</v>
+        <v>9.814393608333333</v>
       </c>
       <c r="P14">
-        <v>29.5167823</v>
+        <v>29.443180825</v>
       </c>
       <c r="Q14">
-        <v>50.8167823</v>
+        <v>50.743180825</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09864463256409983</v>
+        <v>0.0991142791386119</v>
       </c>
       <c r="T14">
-        <v>1.030040248337172</v>
+        <v>1.039194534227122</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.41960006009843</v>
+        <v>31.77193851701394</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09113367285059235</v>
+        <v>0.09093306904477688</v>
       </c>
       <c r="C15">
-        <v>160.5810310864823</v>
+        <v>158.8525804638774</v>
       </c>
       <c r="D15">
-        <v>154.8440310864823</v>
+        <v>155.0665804638774</v>
       </c>
       <c r="E15">
-        <v>-145.937</v>
+        <v>-143.986</v>
       </c>
       <c r="F15">
-        <v>25.363</v>
+        <v>27.31400000000001</v>
       </c>
       <c r="G15">
         <v>31.1</v>
@@ -2511,28 +2511,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M15">
-        <v>1.2757589</v>
+        <v>1.3738942</v>
       </c>
       <c r="N15">
-        <v>39.25757443333333</v>
+        <v>39.15943913333333</v>
       </c>
       <c r="O15">
-        <v>9.814393608333333</v>
+        <v>9.789859783333332</v>
       </c>
       <c r="P15">
-        <v>29.443180825</v>
+        <v>29.36957935</v>
       </c>
       <c r="Q15">
-        <v>50.743180825</v>
+        <v>50.66957934999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0991142791386119</v>
+        <v>0.09959484772648475</v>
       </c>
       <c r="T15">
-        <v>1.039194534227122</v>
+        <v>1.048561710486606</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.77193851701394</v>
+        <v>29.50251433722722</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09093306904477688</v>
+        <v>0.09073246523896139</v>
       </c>
       <c r="C16">
-        <v>158.8525804638774</v>
+        <v>157.1247704796214</v>
       </c>
       <c r="D16">
-        <v>155.0665804638774</v>
+        <v>155.2897704796215</v>
       </c>
       <c r="E16">
-        <v>-143.986</v>
+        <v>-142.035</v>
       </c>
       <c r="F16">
-        <v>27.31400000000001</v>
+        <v>29.26500000000001</v>
       </c>
       <c r="G16">
         <v>31.1</v>
@@ -2593,28 +2593,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M16">
-        <v>1.3738942</v>
+        <v>1.4720295</v>
       </c>
       <c r="N16">
-        <v>39.15943913333333</v>
+        <v>39.06130383333333</v>
       </c>
       <c r="O16">
-        <v>9.789859783333332</v>
+        <v>9.765325958333333</v>
       </c>
       <c r="P16">
-        <v>29.36957935</v>
+        <v>29.295977875</v>
       </c>
       <c r="Q16">
-        <v>50.66957934999999</v>
+        <v>50.595977875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09959484772648475</v>
+        <v>0.1000867238105428</v>
       </c>
       <c r="T16">
-        <v>1.048561710486606</v>
+        <v>1.058149290893372</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.50251433722722</v>
+        <v>27.53568004807874</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09073246523896139</v>
+        <v>0.09053186143314589</v>
       </c>
       <c r="C17">
-        <v>157.1247704796215</v>
+        <v>155.3976039039474</v>
       </c>
       <c r="D17">
-        <v>155.2897704796215</v>
+        <v>155.5136039039474</v>
       </c>
       <c r="E17">
-        <v>-142.035</v>
+        <v>-140.084</v>
       </c>
       <c r="F17">
-        <v>29.265</v>
+        <v>31.216</v>
       </c>
       <c r="G17">
         <v>31.1</v>
@@ -2675,28 +2675,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M17">
-        <v>1.4720295</v>
+        <v>1.5701648</v>
       </c>
       <c r="N17">
-        <v>39.06130383333333</v>
+        <v>38.96316853333333</v>
       </c>
       <c r="O17">
-        <v>9.765325958333333</v>
+        <v>9.740792133333333</v>
       </c>
       <c r="P17">
-        <v>29.295977875</v>
+        <v>29.2223764</v>
       </c>
       <c r="Q17">
-        <v>50.595977875</v>
+        <v>50.5223764</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1000867238105428</v>
+        <v>0.1005903112299356</v>
       </c>
       <c r="T17">
-        <v>1.058149290893372</v>
+        <v>1.067965147024108</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.53568004807875</v>
+        <v>25.81470004507382</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09053186143314589</v>
+        <v>0.09033125762733041</v>
       </c>
       <c r="C18">
-        <v>155.3976039039474</v>
+        <v>153.671083523083</v>
       </c>
       <c r="D18">
-        <v>155.5136039039474</v>
+        <v>155.738083523083</v>
       </c>
       <c r="E18">
-        <v>-140.084</v>
+        <v>-138.133</v>
       </c>
       <c r="F18">
-        <v>31.216</v>
+        <v>33.16700000000001</v>
       </c>
       <c r="G18">
         <v>31.1</v>
@@ -2757,28 +2757,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M18">
-        <v>1.5701648</v>
+        <v>1.6683001</v>
       </c>
       <c r="N18">
-        <v>38.96316853333333</v>
+        <v>38.86503323333333</v>
       </c>
       <c r="O18">
-        <v>9.740792133333333</v>
+        <v>9.716258308333332</v>
       </c>
       <c r="P18">
-        <v>29.2223764</v>
+        <v>29.148774925</v>
       </c>
       <c r="Q18">
-        <v>50.5223764</v>
+        <v>50.448774925</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1005903112299356</v>
+        <v>0.1011060332859403</v>
       </c>
       <c r="T18">
-        <v>1.067965147024108</v>
+        <v>1.078017529808597</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.81470004507382</v>
+        <v>24.29618827771653</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09033125762733041</v>
+        <v>0.09013065382151493</v>
       </c>
       <c r="C19">
-        <v>153.671083523083</v>
+        <v>151.9452121393669</v>
       </c>
       <c r="D19">
-        <v>155.738083523083</v>
+        <v>155.9632121393669</v>
       </c>
       <c r="E19">
-        <v>-138.133</v>
+        <v>-136.182</v>
       </c>
       <c r="F19">
-        <v>33.16700000000001</v>
+        <v>35.11800000000001</v>
       </c>
       <c r="G19">
         <v>31.1</v>
@@ -2839,28 +2839,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M19">
-        <v>1.6683001</v>
+        <v>1.7664354</v>
       </c>
       <c r="N19">
-        <v>38.86503323333333</v>
+        <v>38.76689793333333</v>
       </c>
       <c r="O19">
-        <v>9.716258308333332</v>
+        <v>9.691724483333333</v>
       </c>
       <c r="P19">
-        <v>29.148774925</v>
+        <v>29.07517345</v>
       </c>
       <c r="Q19">
-        <v>50.448774925</v>
+        <v>50.37517345000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1011060332859403</v>
+        <v>0.1016343339286767</v>
       </c>
       <c r="T19">
-        <v>1.078017529808597</v>
+        <v>1.088315092661</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.29618827771653</v>
+        <v>22.94640004006562</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09013065382151494</v>
+        <v>0.08993005001569947</v>
       </c>
       <c r="C20">
-        <v>151.9452121393669</v>
+        <v>150.2199925713647</v>
       </c>
       <c r="D20">
-        <v>155.9632121393669</v>
+        <v>156.1889925713648</v>
       </c>
       <c r="E20">
-        <v>-136.182</v>
+        <v>-134.231</v>
       </c>
       <c r="F20">
-        <v>35.118</v>
+        <v>37.069</v>
       </c>
       <c r="G20">
         <v>31.1</v>
@@ -2921,28 +2921,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M20">
-        <v>1.7664354</v>
+        <v>1.8645707</v>
       </c>
       <c r="N20">
-        <v>38.76689793333333</v>
+        <v>38.66876263333333</v>
       </c>
       <c r="O20">
-        <v>9.691724483333333</v>
+        <v>9.667190658333332</v>
       </c>
       <c r="P20">
-        <v>29.07517345</v>
+        <v>29.001571975</v>
       </c>
       <c r="Q20">
-        <v>50.37517345000001</v>
+        <v>50.301571975</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1016343339286767</v>
+        <v>0.1021756790317277</v>
       </c>
       <c r="T20">
-        <v>1.088315092661</v>
+        <v>1.098866916324574</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.94640004006562</v>
+        <v>21.73869477479901</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08993005001569947</v>
+        <v>0.08972944620988396</v>
       </c>
       <c r="C21">
-        <v>150.2199925713647</v>
+        <v>148.4954276539873</v>
       </c>
       <c r="D21">
-        <v>156.1889925713648</v>
+        <v>156.4154276539873</v>
       </c>
       <c r="E21">
-        <v>-134.231</v>
+        <v>-132.28</v>
       </c>
       <c r="F21">
-        <v>37.069</v>
+        <v>39.02000000000001</v>
       </c>
       <c r="G21">
         <v>31.1</v>
@@ -3003,28 +3003,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M21">
-        <v>1.8645707</v>
+        <v>1.962706000000001</v>
       </c>
       <c r="N21">
-        <v>38.66876263333333</v>
+        <v>38.57062733333333</v>
       </c>
       <c r="O21">
-        <v>9.667190658333332</v>
+        <v>9.642656833333334</v>
       </c>
       <c r="P21">
-        <v>29.001571975</v>
+        <v>28.9279705</v>
       </c>
       <c r="Q21">
-        <v>50.301571975</v>
+        <v>50.2279705</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1021756790317277</v>
+        <v>0.102730557762355</v>
       </c>
       <c r="T21">
-        <v>1.098866916324574</v>
+        <v>1.109682535579737</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.73869477479901</v>
+        <v>20.65176003605906</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08972944620988396</v>
+        <v>0.08952884240406848</v>
       </c>
       <c r="C22">
-        <v>148.4954276539873</v>
+        <v>146.7715202386086</v>
       </c>
       <c r="D22">
-        <v>156.4154276539873</v>
+        <v>156.6425202386086</v>
       </c>
       <c r="E22">
-        <v>-132.28</v>
+        <v>-130.329</v>
       </c>
       <c r="F22">
-        <v>39.02000000000001</v>
+        <v>40.97100000000001</v>
       </c>
       <c r="G22">
         <v>31.1</v>
@@ -3085,28 +3085,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M22">
-        <v>1.962706000000001</v>
+        <v>2.0608413</v>
       </c>
       <c r="N22">
-        <v>38.57062733333333</v>
+        <v>38.47249203333333</v>
       </c>
       <c r="O22">
-        <v>9.642656833333334</v>
+        <v>9.618123008333333</v>
       </c>
       <c r="P22">
-        <v>28.9279705</v>
+        <v>28.854369025</v>
       </c>
       <c r="Q22">
-        <v>50.2279705</v>
+        <v>50.15436902499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.102730557762355</v>
+        <v>0.1032994840557829</v>
       </c>
       <c r="T22">
-        <v>1.109682535579737</v>
+        <v>1.120771967980601</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.65176003605906</v>
+        <v>19.66834289148482</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08952884240406847</v>
+        <v>0.08932823859825301</v>
       </c>
       <c r="C23">
-        <v>146.7715202386086</v>
+        <v>145.0482731931861</v>
       </c>
       <c r="D23">
-        <v>156.6425202386087</v>
+        <v>156.8702731931861</v>
       </c>
       <c r="E23">
-        <v>-130.329</v>
+        <v>-128.378</v>
       </c>
       <c r="F23">
-        <v>40.971</v>
+        <v>42.922</v>
       </c>
       <c r="G23">
         <v>31.1</v>
@@ -3167,28 +3167,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M23">
-        <v>2.0608413</v>
+        <v>2.1589766</v>
       </c>
       <c r="N23">
-        <v>38.47249203333333</v>
+        <v>38.37435673333333</v>
       </c>
       <c r="O23">
-        <v>9.618123008333333</v>
+        <v>9.593589183333332</v>
       </c>
       <c r="P23">
-        <v>28.854369025</v>
+        <v>28.78076755</v>
       </c>
       <c r="Q23">
-        <v>50.15436902499999</v>
+        <v>50.08076755</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1032994840557829</v>
+        <v>0.1038829982028885</v>
       </c>
       <c r="T23">
-        <v>1.120771967980601</v>
+        <v>1.132145744801999</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.66834289148482</v>
+        <v>18.77432730550823</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08932823859825301</v>
+        <v>0.08912763479243752</v>
       </c>
       <c r="C24">
-        <v>145.0482731931861</v>
+        <v>143.325689402381</v>
       </c>
       <c r="D24">
-        <v>156.8702731931861</v>
+        <v>157.098689402381</v>
       </c>
       <c r="E24">
-        <v>-128.378</v>
+        <v>-126.427</v>
       </c>
       <c r="F24">
-        <v>42.922</v>
+        <v>44.873</v>
       </c>
       <c r="G24">
         <v>31.1</v>
@@ -3249,28 +3249,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M24">
-        <v>2.1589766</v>
+        <v>2.2571119</v>
       </c>
       <c r="N24">
-        <v>38.37435673333333</v>
+        <v>38.27622143333333</v>
       </c>
       <c r="O24">
-        <v>9.593589183333332</v>
+        <v>9.569055358333333</v>
       </c>
       <c r="P24">
-        <v>28.78076755</v>
+        <v>28.707166075</v>
       </c>
       <c r="Q24">
-        <v>50.08076755</v>
+        <v>50.007166075</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1038829982028885</v>
+        <v>0.1044816685616072</v>
       </c>
       <c r="T24">
-        <v>1.132145744801999</v>
+        <v>1.143814944397979</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.77432730550823</v>
+        <v>17.95805220526875</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08912763479243752</v>
+        <v>0.08892703098662205</v>
       </c>
       <c r="C25">
-        <v>143.325689402381</v>
+        <v>141.6037717676803</v>
       </c>
       <c r="D25">
-        <v>157.098689402381</v>
+        <v>157.3277717676803</v>
       </c>
       <c r="E25">
-        <v>-126.427</v>
+        <v>-124.476</v>
       </c>
       <c r="F25">
-        <v>44.873</v>
+        <v>46.82400000000001</v>
       </c>
       <c r="G25">
         <v>31.1</v>
@@ -3331,28 +3331,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M25">
-        <v>2.2571119</v>
+        <v>2.3552472</v>
       </c>
       <c r="N25">
-        <v>38.27622143333333</v>
+        <v>38.17808613333333</v>
       </c>
       <c r="O25">
-        <v>9.569055358333333</v>
+        <v>9.544521533333333</v>
       </c>
       <c r="P25">
-        <v>28.707166075</v>
+        <v>28.6335646</v>
       </c>
       <c r="Q25">
-        <v>50.007166075</v>
+        <v>49.9335646</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1044816685616072</v>
+        <v>0.1050960934034501</v>
       </c>
       <c r="T25">
-        <v>1.143814944397979</v>
+        <v>1.155791228193854</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.95805220526875</v>
+        <v>17.20980003004921</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08892703098662204</v>
+        <v>0.08872642718080655</v>
       </c>
       <c r="C26">
-        <v>141.6037717676803</v>
+        <v>139.8825232075198</v>
       </c>
       <c r="D26">
-        <v>157.3277717676804</v>
+        <v>157.5575232075198</v>
       </c>
       <c r="E26">
-        <v>-124.476</v>
+        <v>-122.525</v>
       </c>
       <c r="F26">
-        <v>46.82400000000001</v>
+        <v>48.77500000000001</v>
       </c>
       <c r="G26">
         <v>31.1</v>
@@ -3413,28 +3413,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M26">
-        <v>2.3552472</v>
+        <v>2.4533825</v>
       </c>
       <c r="N26">
-        <v>38.17808613333333</v>
+        <v>38.07995083333333</v>
       </c>
       <c r="O26">
-        <v>9.544521533333333</v>
+        <v>9.519987708333332</v>
       </c>
       <c r="P26">
-        <v>28.6335646</v>
+        <v>28.559963125</v>
       </c>
       <c r="Q26">
-        <v>49.9335646</v>
+        <v>49.85996312499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1050960934034501</v>
+        <v>0.1057269029077421</v>
       </c>
       <c r="T26">
-        <v>1.155791228193854</v>
+        <v>1.168086879557618</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.20980003004922</v>
+        <v>16.52140802884725</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08872642718080655</v>
+        <v>0.08852582337499106</v>
       </c>
       <c r="C27">
-        <v>139.8825232075198</v>
+        <v>138.1619466574075</v>
       </c>
       <c r="D27">
-        <v>157.5575232075198</v>
+        <v>157.7879466574075</v>
       </c>
       <c r="E27">
-        <v>-122.525</v>
+        <v>-120.574</v>
       </c>
       <c r="F27">
-        <v>48.77500000000001</v>
+        <v>50.72600000000001</v>
       </c>
       <c r="G27">
         <v>31.1</v>
@@ -3495,28 +3495,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M27">
-        <v>2.4533825</v>
+        <v>2.5515178</v>
       </c>
       <c r="N27">
-        <v>38.07995083333333</v>
+        <v>37.98181553333333</v>
       </c>
       <c r="O27">
-        <v>9.519987708333332</v>
+        <v>9.495453883333333</v>
       </c>
       <c r="P27">
-        <v>28.559963125</v>
+        <v>28.48636165</v>
       </c>
       <c r="Q27">
-        <v>49.85996312499999</v>
+        <v>49.78636165</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1057269029077421</v>
+        <v>0.1063747613175555</v>
       </c>
       <c r="T27">
-        <v>1.168086879557618</v>
+        <v>1.180714845823106</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.52140802884725</v>
+        <v>15.88596925850697</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08852582337499106</v>
+        <v>0.08832521956917556</v>
       </c>
       <c r="C28">
-        <v>138.1619466574075</v>
+        <v>136.4420450700491</v>
       </c>
       <c r="D28">
-        <v>157.7879466574075</v>
+        <v>158.0190450700491</v>
       </c>
       <c r="E28">
-        <v>-120.574</v>
+        <v>-118.623</v>
       </c>
       <c r="F28">
-        <v>50.72600000000001</v>
+        <v>52.67700000000001</v>
       </c>
       <c r="G28">
         <v>31.1</v>
@@ -3577,28 +3577,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M28">
-        <v>2.5515178</v>
+        <v>2.6496531</v>
       </c>
       <c r="N28">
-        <v>37.98181553333333</v>
+        <v>37.88368023333333</v>
       </c>
       <c r="O28">
-        <v>9.495453883333333</v>
+        <v>9.470920058333332</v>
       </c>
       <c r="P28">
-        <v>28.48636165</v>
+        <v>28.412760175</v>
       </c>
       <c r="Q28">
-        <v>49.78636165</v>
+        <v>49.712760175</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1063747613175555</v>
+        <v>0.1070403692728433</v>
       </c>
       <c r="T28">
-        <v>1.180714845823106</v>
+        <v>1.1936887837671</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.88596925850697</v>
+        <v>15.29760002671041</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08832521956917556</v>
+        <v>0.0881246157633601</v>
       </c>
       <c r="C29">
-        <v>136.4420450700491</v>
+        <v>134.7228214154739</v>
       </c>
       <c r="D29">
-        <v>158.0190450700491</v>
+        <v>158.250821415474</v>
       </c>
       <c r="E29">
-        <v>-118.623</v>
+        <v>-116.672</v>
       </c>
       <c r="F29">
-        <v>52.67700000000001</v>
+        <v>54.62800000000001</v>
       </c>
       <c r="G29">
         <v>31.1</v>
@@ -3659,28 +3659,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M29">
-        <v>2.6496531</v>
+        <v>2.747788400000001</v>
       </c>
       <c r="N29">
-        <v>37.88368023333333</v>
+        <v>37.78554493333333</v>
       </c>
       <c r="O29">
-        <v>9.470920058333332</v>
+        <v>9.446386233333333</v>
       </c>
       <c r="P29">
-        <v>28.412760175</v>
+        <v>28.3391587</v>
       </c>
       <c r="Q29">
-        <v>49.712760175</v>
+        <v>49.6391587</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1070403692728433</v>
+        <v>0.1077244663380001</v>
       </c>
       <c r="T29">
-        <v>1.1936887837671</v>
+        <v>1.207023108876205</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.29760002671041</v>
+        <v>14.75125716861361</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0881246157633601</v>
+        <v>0.08792401195754461</v>
       </c>
       <c r="C30">
-        <v>134.7228214154739</v>
+        <v>133.0042786811623</v>
       </c>
       <c r="D30">
-        <v>158.250821415474</v>
+        <v>158.4832786811623</v>
       </c>
       <c r="E30">
-        <v>-116.672</v>
+        <v>-114.721</v>
       </c>
       <c r="F30">
-        <v>54.62800000000001</v>
+        <v>56.57900000000001</v>
       </c>
       <c r="G30">
         <v>31.1</v>
@@ -3741,28 +3741,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M30">
-        <v>2.747788400000001</v>
+        <v>2.845923700000001</v>
       </c>
       <c r="N30">
-        <v>37.78554493333333</v>
+        <v>37.68740963333333</v>
       </c>
       <c r="O30">
-        <v>9.446386233333333</v>
+        <v>9.421852408333333</v>
       </c>
       <c r="P30">
-        <v>28.3391587</v>
+        <v>28.265557225</v>
       </c>
       <c r="Q30">
-        <v>49.6391587</v>
+        <v>49.565557225</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1077244663380001</v>
+        <v>0.1084278337430206</v>
       </c>
       <c r="T30">
-        <v>1.207023108876205</v>
+        <v>1.220733048777116</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.75125716861361</v>
+        <v>14.24259312831659</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08792401195754461</v>
+        <v>0.08772340815172912</v>
       </c>
       <c r="C31">
-        <v>133.0042786811623</v>
+        <v>131.2864198721737</v>
       </c>
       <c r="D31">
-        <v>158.4832786811623</v>
+        <v>158.7164198721737</v>
       </c>
       <c r="E31">
-        <v>-114.721</v>
+        <v>-112.77</v>
       </c>
       <c r="F31">
-        <v>56.579</v>
+        <v>58.53</v>
       </c>
       <c r="G31">
         <v>31.1</v>
@@ -3823,28 +3823,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M31">
-        <v>2.8459237</v>
+        <v>2.944059</v>
       </c>
       <c r="N31">
-        <v>37.68740963333333</v>
+        <v>37.58927433333333</v>
       </c>
       <c r="O31">
-        <v>9.421852408333333</v>
+        <v>9.397318583333332</v>
       </c>
       <c r="P31">
-        <v>28.265557225</v>
+        <v>28.19195575</v>
       </c>
       <c r="Q31">
-        <v>49.565557225</v>
+        <v>49.49195575</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1084278337430206</v>
+        <v>0.109151297359613</v>
       </c>
       <c r="T31">
-        <v>1.220733048777116</v>
+        <v>1.234834701246625</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.24259312831659</v>
+        <v>13.76784002403937</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08772340815172912</v>
+        <v>0.08752280434591363</v>
       </c>
       <c r="C32">
-        <v>131.2864198721737</v>
+        <v>129.5692480112763</v>
       </c>
       <c r="D32">
-        <v>158.7164198721737</v>
+        <v>158.9502480112763</v>
       </c>
       <c r="E32">
-        <v>-112.77</v>
+        <v>-110.819</v>
       </c>
       <c r="F32">
-        <v>58.53</v>
+        <v>60.48100000000001</v>
       </c>
       <c r="G32">
         <v>31.1</v>
@@ -3905,28 +3905,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M32">
-        <v>2.944059</v>
+        <v>3.0421943</v>
       </c>
       <c r="N32">
-        <v>37.58927433333333</v>
+        <v>37.49113903333333</v>
       </c>
       <c r="O32">
-        <v>9.397318583333332</v>
+        <v>9.372784758333333</v>
       </c>
       <c r="P32">
-        <v>28.19195575</v>
+        <v>28.118354275</v>
       </c>
       <c r="Q32">
-        <v>49.49195575</v>
+        <v>49.418354275</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.109151297359613</v>
+        <v>0.1098957309361067</v>
       </c>
       <c r="T32">
-        <v>1.234834701246625</v>
+        <v>1.249345097265974</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.76784002403937</v>
+        <v>13.32371615229617</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08752280434591363</v>
+        <v>0.08732220054009815</v>
       </c>
       <c r="C33">
-        <v>129.5692480112763</v>
+        <v>127.8527661390778</v>
       </c>
       <c r="D33">
-        <v>158.9502480112763</v>
+        <v>159.1847661390779</v>
       </c>
       <c r="E33">
-        <v>-110.819</v>
+        <v>-108.868</v>
       </c>
       <c r="F33">
-        <v>60.48100000000001</v>
+        <v>62.43200000000001</v>
       </c>
       <c r="G33">
         <v>31.1</v>
@@ -3987,28 +3987,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M33">
-        <v>3.0421943</v>
+        <v>3.1403296</v>
       </c>
       <c r="N33">
-        <v>37.49113903333333</v>
+        <v>37.39300373333333</v>
       </c>
       <c r="O33">
-        <v>9.372784758333333</v>
+        <v>9.348250933333333</v>
       </c>
       <c r="P33">
-        <v>28.118354275</v>
+        <v>28.0447528</v>
       </c>
       <c r="Q33">
-        <v>49.418354275</v>
+        <v>49.34475279999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1098957309361067</v>
+        <v>0.1106620596177914</v>
       </c>
       <c r="T33">
-        <v>1.249345097265974</v>
+        <v>1.264282269638834</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.32371615229617</v>
+        <v>12.90735002253691</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08732220054009815</v>
+        <v>0.08749284673428268</v>
       </c>
       <c r="C34">
-        <v>127.8527661390778</v>
+        <v>125.7022263921636</v>
       </c>
       <c r="D34">
-        <v>159.1847661390779</v>
+        <v>158.9852263921636</v>
       </c>
       <c r="E34">
-        <v>-108.868</v>
+        <v>-106.917</v>
       </c>
       <c r="F34">
-        <v>62.43200000000001</v>
+        <v>64.38300000000001</v>
       </c>
       <c r="G34">
         <v>31.1</v>
@@ -4069,45 +4069,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M34">
-        <v>3.1403296</v>
+        <v>3.3350394</v>
       </c>
       <c r="N34">
-        <v>37.39300373333333</v>
+        <v>37.19829393333333</v>
       </c>
       <c r="O34">
-        <v>9.348250933333333</v>
+        <v>9.299573483333333</v>
       </c>
       <c r="P34">
-        <v>28.0447528</v>
+        <v>27.89872045</v>
       </c>
       <c r="Q34">
-        <v>49.34475279999999</v>
+        <v>49.19872045</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1106620596177914</v>
+        <v>0.1114512637825115</v>
       </c>
       <c r="T34">
-        <v>1.264282269638834</v>
+        <v>1.279665327754167</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>12.90735002253691</v>
+        <v>12.15377945260057</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08749284673428268</v>
+        <v>0.08730349292846717</v>
       </c>
       <c r="C35">
-        <v>125.7022263921636</v>
+        <v>123.9726717641075</v>
       </c>
       <c r="D35">
-        <v>158.9852263921636</v>
+        <v>159.2066717641075</v>
       </c>
       <c r="E35">
-        <v>-106.917</v>
+        <v>-104.966</v>
       </c>
       <c r="F35">
-        <v>64.38300000000001</v>
+        <v>66.33400000000002</v>
       </c>
       <c r="G35">
         <v>31.1</v>
@@ -4151,28 +4151,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M35">
-        <v>3.3350394</v>
+        <v>3.436101200000001</v>
       </c>
       <c r="N35">
-        <v>37.19829393333333</v>
+        <v>37.09723213333333</v>
       </c>
       <c r="O35">
-        <v>9.299573483333333</v>
+        <v>9.274308033333332</v>
       </c>
       <c r="P35">
-        <v>27.89872045</v>
+        <v>27.82292409999999</v>
       </c>
       <c r="Q35">
-        <v>49.19872045</v>
+        <v>49.12292409999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1114512637825115</v>
+        <v>0.1122643832249503</v>
       </c>
       <c r="T35">
-        <v>1.279665327754167</v>
+        <v>1.295514539145722</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.15377945260057</v>
+        <v>11.79631535105349</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08730349292846717</v>
+        <v>0.0871141391226517</v>
       </c>
       <c r="C36">
-        <v>123.9726717641075</v>
+        <v>122.2437348846644</v>
       </c>
       <c r="D36">
-        <v>159.2066717641075</v>
+        <v>159.4287348846644</v>
       </c>
       <c r="E36">
-        <v>-104.966</v>
+        <v>-103.015</v>
       </c>
       <c r="F36">
-        <v>66.33400000000002</v>
+        <v>68.28500000000001</v>
       </c>
       <c r="G36">
         <v>31.1</v>
@@ -4233,28 +4233,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M36">
-        <v>3.436101200000001</v>
+        <v>3.537163000000001</v>
       </c>
       <c r="N36">
-        <v>37.09723213333333</v>
+        <v>36.99617033333333</v>
       </c>
       <c r="O36">
-        <v>9.274308033333332</v>
+        <v>9.249042583333333</v>
       </c>
       <c r="P36">
-        <v>27.82292409999999</v>
+        <v>27.74712775</v>
       </c>
       <c r="Q36">
-        <v>49.12292409999999</v>
+        <v>49.04712775</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1122643832249503</v>
+        <v>0.1131025217271565</v>
       </c>
       <c r="T36">
-        <v>1.295514539145722</v>
+        <v>1.311851418580094</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.79631535105349</v>
+        <v>11.45927776959482</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0871141391226517</v>
+        <v>0.08692478531683621</v>
       </c>
       <c r="C37">
-        <v>122.2437348846644</v>
+        <v>120.5154183423713</v>
       </c>
       <c r="D37">
-        <v>159.4287348846644</v>
+        <v>159.6514183423713</v>
       </c>
       <c r="E37">
-        <v>-103.015</v>
+        <v>-101.064</v>
       </c>
       <c r="F37">
-        <v>68.28500000000001</v>
+        <v>70.23600000000002</v>
       </c>
       <c r="G37">
         <v>31.1</v>
@@ -4315,28 +4315,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M37">
-        <v>3.537163000000001</v>
+        <v>3.638224800000001</v>
       </c>
       <c r="N37">
-        <v>36.99617033333333</v>
+        <v>36.89510853333333</v>
       </c>
       <c r="O37">
-        <v>9.249042583333333</v>
+        <v>9.223777133333332</v>
       </c>
       <c r="P37">
-        <v>27.74712775</v>
+        <v>27.6713314</v>
       </c>
       <c r="Q37">
-        <v>49.04712775</v>
+        <v>48.9713314</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1131025217271565</v>
+        <v>0.1139668520575566</v>
       </c>
       <c r="T37">
-        <v>1.311851418580094</v>
+        <v>1.328698825496791</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.45927776959482</v>
+        <v>11.14096449821719</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08692478531683623</v>
+        <v>0.08673543151102074</v>
       </c>
       <c r="C38">
-        <v>120.5154183423713</v>
+        <v>118.7877247402477</v>
       </c>
       <c r="D38">
-        <v>159.6514183423713</v>
+        <v>159.8747247402478</v>
       </c>
       <c r="E38">
-        <v>-101.064</v>
+        <v>-99.113</v>
       </c>
       <c r="F38">
-        <v>70.236</v>
+        <v>72.18700000000001</v>
       </c>
       <c r="G38">
         <v>31.1</v>
@@ -4397,28 +4397,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M38">
-        <v>3.6382248</v>
+        <v>3.739286600000001</v>
       </c>
       <c r="N38">
-        <v>36.89510853333333</v>
+        <v>36.79404673333333</v>
       </c>
       <c r="O38">
-        <v>9.223777133333332</v>
+        <v>9.198511683333333</v>
       </c>
       <c r="P38">
-        <v>27.6713314</v>
+        <v>27.59553505</v>
       </c>
       <c r="Q38">
-        <v>48.9713314</v>
+        <v>48.89553505</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1139668520575566</v>
+        <v>0.1148586214460647</v>
       </c>
       <c r="T38">
-        <v>1.328698825496791</v>
+        <v>1.346081070728303</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.14096449821719</v>
+        <v>10.83985734961672</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08673543151102074</v>
+        <v>0.08654607770520525</v>
       </c>
       <c r="C39">
-        <v>118.7877247402477</v>
+        <v>117.0606566958973</v>
       </c>
       <c r="D39">
-        <v>159.8747247402478</v>
+        <v>160.0986566958973</v>
       </c>
       <c r="E39">
-        <v>-99.113</v>
+        <v>-97.16200000000001</v>
       </c>
       <c r="F39">
-        <v>72.18700000000001</v>
+        <v>74.13800000000001</v>
       </c>
       <c r="G39">
         <v>31.1</v>
@@ -4479,28 +4479,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M39">
-        <v>3.739286600000001</v>
+        <v>3.8403484</v>
       </c>
       <c r="N39">
-        <v>36.79404673333333</v>
+        <v>36.69298493333333</v>
       </c>
       <c r="O39">
-        <v>9.198511683333333</v>
+        <v>9.173246233333332</v>
       </c>
       <c r="P39">
-        <v>27.59553505</v>
+        <v>27.5197387</v>
       </c>
       <c r="Q39">
-        <v>48.89553505</v>
+        <v>48.8197387</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1148586214460647</v>
+        <v>0.1157791575890407</v>
       </c>
       <c r="T39">
-        <v>1.346081070728303</v>
+        <v>1.364024033547928</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.83985734961672</v>
+        <v>10.55459794567944</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08654607770520525</v>
+        <v>0.08635672389938978</v>
       </c>
       <c r="C40">
-        <v>117.0606566958973</v>
+        <v>115.3342168416093</v>
       </c>
       <c r="D40">
-        <v>160.0986566958973</v>
+        <v>160.3232168416094</v>
       </c>
       <c r="E40">
-        <v>-97.16200000000001</v>
+        <v>-95.211</v>
       </c>
       <c r="F40">
-        <v>74.13800000000001</v>
+        <v>76.08900000000001</v>
       </c>
       <c r="G40">
         <v>31.1</v>
@@ -4561,28 +4561,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M40">
-        <v>3.8403484</v>
+        <v>3.9414102</v>
       </c>
       <c r="N40">
-        <v>36.69298493333333</v>
+        <v>36.59192313333333</v>
       </c>
       <c r="O40">
-        <v>9.173246233333332</v>
+        <v>9.147980783333333</v>
       </c>
       <c r="P40">
-        <v>27.5197387</v>
+        <v>27.44394235</v>
       </c>
       <c r="Q40">
-        <v>48.8197387</v>
+        <v>48.74394235</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1157791575890407</v>
+        <v>0.1167298752449013</v>
       </c>
       <c r="T40">
-        <v>1.364024033547928</v>
+        <v>1.382555290230492</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.55459794567944</v>
+        <v>10.28396722912356</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08635672389938978</v>
+        <v>0.08616737009357428</v>
       </c>
       <c r="C41">
-        <v>115.3342168416093</v>
+        <v>113.6084078244631</v>
       </c>
       <c r="D41">
-        <v>160.3232168416094</v>
+        <v>160.5484078244631</v>
       </c>
       <c r="E41">
-        <v>-95.211</v>
+        <v>-93.25999999999999</v>
       </c>
       <c r="F41">
-        <v>76.08900000000001</v>
+        <v>78.04000000000002</v>
       </c>
       <c r="G41">
         <v>31.1</v>
@@ -4643,28 +4643,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M41">
-        <v>3.9414102</v>
+        <v>4.042472000000001</v>
       </c>
       <c r="N41">
-        <v>36.59192313333333</v>
+        <v>36.49086133333333</v>
       </c>
       <c r="O41">
-        <v>9.147980783333333</v>
+        <v>9.122715333333332</v>
       </c>
       <c r="P41">
-        <v>27.44394235</v>
+        <v>27.368146</v>
       </c>
       <c r="Q41">
-        <v>48.74394235</v>
+        <v>48.66814599999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1167298752449013</v>
+        <v>0.1177122834892905</v>
       </c>
       <c r="T41">
-        <v>1.382555290230492</v>
+        <v>1.401704255469142</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.28396722912356</v>
+        <v>10.02686804839547</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08616737009357428</v>
+        <v>0.08650076628775881</v>
       </c>
       <c r="C42">
-        <v>113.6084078244631</v>
+        <v>111.261335539257</v>
       </c>
       <c r="D42">
-        <v>160.5484078244631</v>
+        <v>160.152335539257</v>
       </c>
       <c r="E42">
-        <v>-93.25999999999999</v>
+        <v>-91.309</v>
       </c>
       <c r="F42">
-        <v>78.04000000000002</v>
+        <v>79.99100000000001</v>
       </c>
       <c r="G42">
         <v>31.1</v>
@@ -4725,45 +4725,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M42">
-        <v>4.042472000000001</v>
+        <v>4.279518500000001</v>
       </c>
       <c r="N42">
-        <v>36.49086133333333</v>
+        <v>36.25381483333333</v>
       </c>
       <c r="O42">
-        <v>9.122715333333332</v>
+        <v>9.063453708333332</v>
       </c>
       <c r="P42">
-        <v>27.368146</v>
+        <v>27.190361125</v>
       </c>
       <c r="Q42">
-        <v>48.66814599999999</v>
+        <v>48.49036112499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1177122834892905</v>
+        <v>0.1187279937080658</v>
       </c>
       <c r="T42">
-        <v>1.401704255469142</v>
+        <v>1.421502338173508</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>10.02686804839547</v>
+        <v>9.47147052485772</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08650076628775881</v>
+        <v>0.08632416248194331</v>
       </c>
       <c r="C43">
-        <v>111.261335539257</v>
+        <v>109.5198958595773</v>
       </c>
       <c r="D43">
-        <v>160.152335539257</v>
+        <v>160.3618958595773</v>
       </c>
       <c r="E43">
-        <v>-91.309</v>
+        <v>-89.35799999999999</v>
       </c>
       <c r="F43">
-        <v>79.99100000000001</v>
+        <v>81.94200000000002</v>
       </c>
       <c r="G43">
         <v>31.1</v>
@@ -4807,28 +4807,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M43">
-        <v>4.279518500000001</v>
+        <v>4.383897000000001</v>
       </c>
       <c r="N43">
-        <v>36.25381483333333</v>
+        <v>36.14943633333333</v>
       </c>
       <c r="O43">
-        <v>9.063453708333332</v>
+        <v>9.037359083333332</v>
       </c>
       <c r="P43">
-        <v>27.190361125</v>
+        <v>27.11207725</v>
       </c>
       <c r="Q43">
-        <v>48.49036112499999</v>
+        <v>48.41207725</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1187279937080658</v>
+        <v>0.1197787284171437</v>
       </c>
       <c r="T43">
-        <v>1.421502338173508</v>
+        <v>1.441983113384922</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.47147052485772</v>
+        <v>9.245959321884916</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08632416248194333</v>
+        <v>0.08614755867612785</v>
       </c>
       <c r="C44">
-        <v>109.5198958595773</v>
+        <v>107.7790053203986</v>
       </c>
       <c r="D44">
-        <v>160.3618958595773</v>
+        <v>160.5720053203986</v>
       </c>
       <c r="E44">
-        <v>-89.358</v>
+        <v>-87.407</v>
       </c>
       <c r="F44">
-        <v>81.94200000000001</v>
+        <v>83.89300000000001</v>
       </c>
       <c r="G44">
         <v>31.1</v>
@@ -4889,28 +4889,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M44">
-        <v>4.383897</v>
+        <v>4.4882755</v>
       </c>
       <c r="N44">
-        <v>36.14943633333333</v>
+        <v>36.04505783333333</v>
       </c>
       <c r="O44">
-        <v>9.037359083333333</v>
+        <v>9.011264458333333</v>
       </c>
       <c r="P44">
-        <v>27.11207725</v>
+        <v>27.033793375</v>
       </c>
       <c r="Q44">
-        <v>48.41207725</v>
+        <v>48.333793375</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1197787284171437</v>
+        <v>0.1208663310107506</v>
       </c>
       <c r="T44">
-        <v>1.441983113384922</v>
+        <v>1.463182512287964</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.24595932188492</v>
+        <v>9.030937012073641</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08614755867612785</v>
+        <v>0.08597095487031237</v>
       </c>
       <c r="C45">
-        <v>107.7790053203986</v>
+        <v>106.0386660830382</v>
       </c>
       <c r="D45">
-        <v>160.5720053203986</v>
+        <v>160.7826660830382</v>
       </c>
       <c r="E45">
-        <v>-87.407</v>
+        <v>-85.456</v>
       </c>
       <c r="F45">
-        <v>83.89300000000001</v>
+        <v>85.84400000000001</v>
       </c>
       <c r="G45">
         <v>31.1</v>
@@ -4971,28 +4971,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M45">
-        <v>4.4882755</v>
+        <v>4.592654</v>
       </c>
       <c r="N45">
-        <v>36.04505783333333</v>
+        <v>35.94067933333333</v>
       </c>
       <c r="O45">
-        <v>9.011264458333333</v>
+        <v>8.985169833333332</v>
       </c>
       <c r="P45">
-        <v>27.033793375</v>
+        <v>26.9555095</v>
       </c>
       <c r="Q45">
-        <v>48.333793375</v>
+        <v>48.2555095</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1208663310107506</v>
+        <v>0.1219927765541292</v>
       </c>
       <c r="T45">
-        <v>1.463182512287964</v>
+        <v>1.4851390325804</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.030937012073641</v>
+        <v>8.825688443617421</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08597095487031237</v>
+        <v>0.08579435106449687</v>
       </c>
       <c r="C46">
-        <v>106.0386660830382</v>
+        <v>104.2988803201706</v>
       </c>
       <c r="D46">
-        <v>160.7826660830382</v>
+        <v>160.9938803201706</v>
       </c>
       <c r="E46">
-        <v>-85.456</v>
+        <v>-83.505</v>
       </c>
       <c r="F46">
-        <v>85.84400000000001</v>
+        <v>87.79500000000002</v>
       </c>
       <c r="G46">
         <v>31.1</v>
@@ -5053,28 +5053,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M46">
-        <v>4.592654</v>
+        <v>4.697032500000001</v>
       </c>
       <c r="N46">
-        <v>35.94067933333333</v>
+        <v>35.83630083333333</v>
       </c>
       <c r="O46">
-        <v>8.985169833333332</v>
+        <v>8.959075208333333</v>
       </c>
       <c r="P46">
-        <v>26.9555095</v>
+        <v>26.877225625</v>
       </c>
       <c r="Q46">
-        <v>48.2555095</v>
+        <v>48.17722562500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1219927765541292</v>
+        <v>0.1231601837536307</v>
       </c>
       <c r="T46">
-        <v>1.4851390325804</v>
+        <v>1.507893971792561</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.825688443617421</v>
+        <v>8.629562033759257</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08579435106449687</v>
+        <v>0.08561774725868138</v>
       </c>
       <c r="C47">
-        <v>104.2988803201706</v>
+        <v>102.5596502159017</v>
       </c>
       <c r="D47">
-        <v>160.9938803201706</v>
+        <v>161.2056502159017</v>
       </c>
       <c r="E47">
-        <v>-83.505</v>
+        <v>-81.554</v>
       </c>
       <c r="F47">
-        <v>87.79500000000002</v>
+        <v>89.74600000000001</v>
       </c>
       <c r="G47">
         <v>31.1</v>
@@ -5135,28 +5135,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M47">
-        <v>4.697032500000001</v>
+        <v>4.801411000000001</v>
       </c>
       <c r="N47">
-        <v>35.83630083333333</v>
+        <v>35.73192233333333</v>
       </c>
       <c r="O47">
-        <v>8.959075208333333</v>
+        <v>8.932980583333332</v>
       </c>
       <c r="P47">
-        <v>26.877225625</v>
+        <v>26.79894175</v>
       </c>
       <c r="Q47">
-        <v>48.17722562500001</v>
+        <v>48.09894174999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1231601837536307</v>
+        <v>0.1243708282568174</v>
       </c>
       <c r="T47">
-        <v>1.507893971792561</v>
+        <v>1.531491686531099</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.629562033759257</v>
+        <v>8.441962859112316</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08561774725868138</v>
+        <v>0.08544114345286591</v>
       </c>
       <c r="C48">
-        <v>102.5596502159017</v>
+        <v>100.8209779658445</v>
       </c>
       <c r="D48">
-        <v>161.2056502159017</v>
+        <v>161.4179779658445</v>
       </c>
       <c r="E48">
-        <v>-81.554</v>
+        <v>-79.60299999999999</v>
       </c>
       <c r="F48">
-        <v>89.74600000000001</v>
+        <v>91.69700000000002</v>
       </c>
       <c r="G48">
         <v>31.1</v>
@@ -5217,28 +5217,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M48">
-        <v>4.801411000000001</v>
+        <v>4.905789500000001</v>
       </c>
       <c r="N48">
-        <v>35.73192233333333</v>
+        <v>35.62754383333333</v>
       </c>
       <c r="O48">
-        <v>8.932980583333332</v>
+        <v>8.906885958333334</v>
       </c>
       <c r="P48">
-        <v>26.79894175</v>
+        <v>26.720657875</v>
       </c>
       <c r="Q48">
-        <v>48.09894174999999</v>
+        <v>48.020657875</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1243708282568174</v>
+        <v>0.1256271574582375</v>
       </c>
       <c r="T48">
-        <v>1.531491686531099</v>
+        <v>1.555979881071091</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.441962859112316</v>
+        <v>8.262346628067373</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08544114345286591</v>
+        <v>0.08526453964705041</v>
       </c>
       <c r="C49">
-        <v>100.8209779658445</v>
+        <v>99.08286577719497</v>
       </c>
       <c r="D49">
-        <v>161.4179779658445</v>
+        <v>161.630865777195</v>
       </c>
       <c r="E49">
-        <v>-79.60299999999999</v>
+        <v>-77.65199999999999</v>
       </c>
       <c r="F49">
-        <v>91.69700000000002</v>
+        <v>93.64800000000002</v>
       </c>
       <c r="G49">
         <v>31.1</v>
@@ -5299,28 +5299,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M49">
-        <v>4.905789500000001</v>
+        <v>5.010168000000001</v>
       </c>
       <c r="N49">
-        <v>35.62754383333333</v>
+        <v>35.52316533333333</v>
       </c>
       <c r="O49">
-        <v>8.906885958333334</v>
+        <v>8.880791333333333</v>
       </c>
       <c r="P49">
-        <v>26.720657875</v>
+        <v>26.642374</v>
       </c>
       <c r="Q49">
-        <v>48.020657875</v>
+        <v>47.942374</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1256271574582375</v>
+        <v>0.1269318070135585</v>
       </c>
       <c r="T49">
-        <v>1.555979881071091</v>
+        <v>1.581409929247237</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.262346628067373</v>
+        <v>8.090214406649302</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08526453964705041</v>
+        <v>0.08508793584123493</v>
       </c>
       <c r="C50">
-        <v>99.08286577719498</v>
+        <v>97.34531586880819</v>
       </c>
       <c r="D50">
-        <v>161.630865777195</v>
+        <v>161.8443158688082</v>
       </c>
       <c r="E50">
-        <v>-77.652</v>
+        <v>-75.70100000000001</v>
       </c>
       <c r="F50">
-        <v>93.64800000000001</v>
+        <v>95.599</v>
       </c>
       <c r="G50">
         <v>31.1</v>
@@ -5381,28 +5381,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M50">
-        <v>5.010168</v>
+        <v>5.1145465</v>
       </c>
       <c r="N50">
-        <v>35.52316533333333</v>
+        <v>35.41878683333333</v>
       </c>
       <c r="O50">
-        <v>8.880791333333333</v>
+        <v>8.854696708333332</v>
       </c>
       <c r="P50">
-        <v>26.642374</v>
+        <v>26.564090125</v>
       </c>
       <c r="Q50">
-        <v>47.942374</v>
+        <v>47.864090125</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1269318070135585</v>
+        <v>0.1282876192965391</v>
       </c>
       <c r="T50">
-        <v>1.581409929247237</v>
+        <v>1.607837234214604</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.090214406649304</v>
+        <v>7.925107990187072</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08508793584123493</v>
+        <v>0.08491133203541944</v>
       </c>
       <c r="C51">
-        <v>97.34531586880819</v>
+        <v>95.60833047127559</v>
       </c>
       <c r="D51">
-        <v>161.8443158688082</v>
+        <v>162.0583304712756</v>
       </c>
       <c r="E51">
-        <v>-75.70100000000001</v>
+        <v>-73.75</v>
       </c>
       <c r="F51">
-        <v>95.599</v>
+        <v>97.55000000000001</v>
       </c>
       <c r="G51">
         <v>31.1</v>
@@ -5463,28 +5463,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M51">
-        <v>5.1145465</v>
+        <v>5.218925</v>
       </c>
       <c r="N51">
-        <v>35.41878683333333</v>
+        <v>35.31440833333333</v>
       </c>
       <c r="O51">
-        <v>8.854696708333332</v>
+        <v>8.828602083333333</v>
       </c>
       <c r="P51">
-        <v>26.564090125</v>
+        <v>26.48580625</v>
       </c>
       <c r="Q51">
-        <v>47.864090125</v>
+        <v>47.78580625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1282876192965391</v>
+        <v>0.1296976640708389</v>
       </c>
       <c r="T51">
-        <v>1.607837234214604</v>
+        <v>1.635321631380665</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.925107990187072</v>
+        <v>7.766605830383332</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08491133203541944</v>
+        <v>0.08473472822960396</v>
       </c>
       <c r="C52">
-        <v>95.60833047127559</v>
+        <v>93.8719118270029</v>
       </c>
       <c r="D52">
-        <v>162.0583304712756</v>
+        <v>162.2729118270029</v>
       </c>
       <c r="E52">
-        <v>-73.75</v>
+        <v>-71.79899999999999</v>
       </c>
       <c r="F52">
-        <v>97.55000000000001</v>
+        <v>99.50100000000002</v>
       </c>
       <c r="G52">
         <v>31.1</v>
@@ -5545,28 +5545,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M52">
-        <v>5.218925</v>
+        <v>5.323303500000001</v>
       </c>
       <c r="N52">
-        <v>35.31440833333333</v>
+        <v>35.21002983333333</v>
       </c>
       <c r="O52">
-        <v>8.828602083333333</v>
+        <v>8.802507458333332</v>
       </c>
       <c r="P52">
-        <v>26.48580625</v>
+        <v>26.407522375</v>
       </c>
       <c r="Q52">
-        <v>47.78580625</v>
+        <v>47.707522375</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1296976640708389</v>
+        <v>0.1311652616930693</v>
       </c>
       <c r="T52">
-        <v>1.635321631380665</v>
+        <v>1.663927840675954</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.766605830383332</v>
+        <v>7.614319441552285</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08473472822960396</v>
+        <v>0.08487012442378847</v>
       </c>
       <c r="C53">
-        <v>93.8719118270029</v>
+        <v>91.75634874778432</v>
       </c>
       <c r="D53">
-        <v>162.2729118270029</v>
+        <v>162.1083487477843</v>
       </c>
       <c r="E53">
-        <v>-71.79899999999999</v>
+        <v>-69.848</v>
       </c>
       <c r="F53">
-        <v>99.50100000000002</v>
+        <v>101.452</v>
       </c>
       <c r="G53">
         <v>31.1</v>
@@ -5627,45 +5627,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M53">
-        <v>5.323303500000001</v>
+        <v>5.508843600000001</v>
       </c>
       <c r="N53">
-        <v>35.21002983333333</v>
+        <v>35.02448973333333</v>
       </c>
       <c r="O53">
-        <v>8.802507458333332</v>
+        <v>8.756122433333333</v>
       </c>
       <c r="P53">
-        <v>26.407522375</v>
+        <v>26.2683673</v>
       </c>
       <c r="Q53">
-        <v>47.707522375</v>
+        <v>47.56836730000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1311652616930693</v>
+        <v>0.132694009216226</v>
       </c>
       <c r="T53">
-        <v>1.663927840675954</v>
+        <v>1.693725975358546</v>
       </c>
       <c r="U53">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y53">
-        <v>7.614319441552285</v>
+        <v>7.357866056196137</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08487012442378847</v>
+        <v>0.08469952061797299</v>
       </c>
       <c r="C54">
-        <v>91.75634874778432</v>
+        <v>90.01275857020875</v>
       </c>
       <c r="D54">
-        <v>162.1083487477843</v>
+        <v>162.3157585702088</v>
       </c>
       <c r="E54">
-        <v>-69.848</v>
+        <v>-67.89699999999999</v>
       </c>
       <c r="F54">
-        <v>101.452</v>
+        <v>103.403</v>
       </c>
       <c r="G54">
         <v>31.1</v>
@@ -5709,28 +5709,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M54">
-        <v>5.508843600000001</v>
+        <v>5.614782900000002</v>
       </c>
       <c r="N54">
-        <v>35.02448973333333</v>
+        <v>34.91855043333333</v>
       </c>
       <c r="O54">
-        <v>8.756122433333333</v>
+        <v>8.729637608333332</v>
       </c>
       <c r="P54">
-        <v>26.2683673</v>
+        <v>26.188912825</v>
       </c>
       <c r="Q54">
-        <v>47.56836730000001</v>
+        <v>47.488912825</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.132694009216226</v>
+        <v>0.1342878098254745</v>
       </c>
       <c r="T54">
-        <v>1.693725975358546</v>
+        <v>1.724792115772313</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.357866056196137</v>
+        <v>7.219038394758472</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08469952061797299</v>
+        <v>0.0845289168121575</v>
       </c>
       <c r="C55">
-        <v>90.01275857020875</v>
+        <v>88.26969981431273</v>
       </c>
       <c r="D55">
-        <v>162.3157585702088</v>
+        <v>162.5236998143127</v>
       </c>
       <c r="E55">
-        <v>-67.89699999999999</v>
+        <v>-65.946</v>
       </c>
       <c r="F55">
-        <v>103.403</v>
+        <v>105.354</v>
       </c>
       <c r="G55">
         <v>31.1</v>
@@ -5791,28 +5791,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M55">
-        <v>5.614782900000002</v>
+        <v>5.720722200000001</v>
       </c>
       <c r="N55">
-        <v>34.91855043333333</v>
+        <v>34.81261113333333</v>
       </c>
       <c r="O55">
-        <v>8.729637608333332</v>
+        <v>8.703152783333334</v>
       </c>
       <c r="P55">
-        <v>26.188912825</v>
+        <v>26.10945835</v>
       </c>
       <c r="Q55">
-        <v>47.488912825</v>
+        <v>47.40945835</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1342878098254745</v>
+        <v>0.1359509061133859</v>
       </c>
       <c r="T55">
-        <v>1.724792115772313</v>
+        <v>1.7572089579432</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.219038394758472</v>
+        <v>7.085352498559243</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0845289168121575</v>
+        <v>0.08435831300634203</v>
       </c>
       <c r="C56">
-        <v>88.26969981431273</v>
+        <v>86.52717452511446</v>
       </c>
       <c r="D56">
-        <v>162.5236998143127</v>
+        <v>162.7321745251145</v>
       </c>
       <c r="E56">
-        <v>-65.946</v>
+        <v>-63.99499999999999</v>
       </c>
       <c r="F56">
-        <v>105.354</v>
+        <v>107.305</v>
       </c>
       <c r="G56">
         <v>31.1</v>
@@ -5873,28 +5873,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M56">
-        <v>5.720722200000001</v>
+        <v>5.826661500000001</v>
       </c>
       <c r="N56">
-        <v>34.81261113333333</v>
+        <v>34.70667183333333</v>
       </c>
       <c r="O56">
-        <v>8.703152783333334</v>
+        <v>8.676667958333333</v>
       </c>
       <c r="P56">
-        <v>26.10945835</v>
+        <v>26.030003875</v>
       </c>
       <c r="Q56">
-        <v>47.40945835</v>
+        <v>47.330003875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1359509061133859</v>
+        <v>0.1376879177918712</v>
       </c>
       <c r="T56">
-        <v>1.7572089579432</v>
+        <v>1.791066548655015</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.085352498559243</v>
+        <v>6.956527907676347</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08435831300634203</v>
+        <v>0.08418770920052653</v>
       </c>
       <c r="C57">
-        <v>86.52717452511446</v>
+        <v>84.78518475813871</v>
       </c>
       <c r="D57">
-        <v>162.7321745251145</v>
+        <v>162.9411847581387</v>
       </c>
       <c r="E57">
-        <v>-63.99499999999999</v>
+        <v>-62.04399999999998</v>
       </c>
       <c r="F57">
-        <v>107.305</v>
+        <v>109.256</v>
       </c>
       <c r="G57">
         <v>31.1</v>
@@ -5955,28 +5955,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M57">
-        <v>5.826661500000001</v>
+        <v>5.932600800000001</v>
       </c>
       <c r="N57">
-        <v>34.70667183333333</v>
+        <v>34.60073253333333</v>
       </c>
       <c r="O57">
-        <v>8.676667958333333</v>
+        <v>8.650183133333332</v>
       </c>
       <c r="P57">
-        <v>26.030003875</v>
+        <v>25.9505494</v>
       </c>
       <c r="Q57">
-        <v>47.330003875</v>
+        <v>47.2505494</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1376879177918712</v>
+        <v>0.1395038845466512</v>
       </c>
       <c r="T57">
-        <v>1.791066548655015</v>
+        <v>1.826463120762821</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.956527907676347</v>
+        <v>6.832304195039269</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08418770920052653</v>
+        <v>0.08401710539471105</v>
       </c>
       <c r="C58">
-        <v>84.78518475813871</v>
+        <v>83.04373257948393</v>
       </c>
       <c r="D58">
-        <v>162.9411847581387</v>
+        <v>163.150732579484</v>
       </c>
       <c r="E58">
-        <v>-62.04399999999998</v>
+        <v>-60.09299999999999</v>
       </c>
       <c r="F58">
-        <v>109.256</v>
+        <v>111.207</v>
       </c>
       <c r="G58">
         <v>31.1</v>
@@ -6037,28 +6037,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M58">
-        <v>5.932600800000001</v>
+        <v>6.038540100000001</v>
       </c>
       <c r="N58">
-        <v>34.60073253333333</v>
+        <v>34.49479323333333</v>
       </c>
       <c r="O58">
-        <v>8.650183133333332</v>
+        <v>8.623698308333333</v>
       </c>
       <c r="P58">
-        <v>25.9505494</v>
+        <v>25.871094925</v>
       </c>
       <c r="Q58">
-        <v>47.2505494</v>
+        <v>47.17109492500001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1395038845466512</v>
+        <v>0.1414043148714211</v>
       </c>
       <c r="T58">
-        <v>1.826463120762821</v>
+        <v>1.863506045061689</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.832304195039269</v>
+        <v>6.712439209161388</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08401710539471105</v>
+        <v>0.08384650158889558</v>
       </c>
       <c r="C59">
-        <v>83.04373257948393</v>
+        <v>81.30282006589071</v>
       </c>
       <c r="D59">
-        <v>163.150732579484</v>
+        <v>163.3608200658907</v>
       </c>
       <c r="E59">
-        <v>-60.09299999999999</v>
+        <v>-58.14199999999998</v>
       </c>
       <c r="F59">
-        <v>111.207</v>
+        <v>113.158</v>
       </c>
       <c r="G59">
         <v>31.1</v>
@@ -6119,28 +6119,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M59">
-        <v>6.038540100000001</v>
+        <v>6.144479400000002</v>
       </c>
       <c r="N59">
-        <v>34.49479323333333</v>
+        <v>34.38885393333333</v>
       </c>
       <c r="O59">
-        <v>8.623698308333333</v>
+        <v>8.597213483333332</v>
       </c>
       <c r="P59">
-        <v>25.871094925</v>
+        <v>25.79164045</v>
       </c>
       <c r="Q59">
-        <v>47.17109492500001</v>
+        <v>47.09164045</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1414043148714211</v>
+        <v>0.1433952418783228</v>
       </c>
       <c r="T59">
-        <v>1.863506045061689</v>
+        <v>1.902312918136693</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.712439209161388</v>
+        <v>6.596707498658605</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08384650158889556</v>
+        <v>0.08367589778308009</v>
       </c>
       <c r="C60">
-        <v>81.30282006589074</v>
+        <v>79.56244930481014</v>
       </c>
       <c r="D60">
-        <v>163.3608200658907</v>
+        <v>163.5714493048102</v>
       </c>
       <c r="E60">
-        <v>-58.14200000000001</v>
+        <v>-56.191</v>
       </c>
       <c r="F60">
-        <v>113.158</v>
+        <v>115.109</v>
       </c>
       <c r="G60">
         <v>31.1</v>
@@ -6201,28 +6201,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M60">
-        <v>6.1444794</v>
+        <v>6.250418700000001</v>
       </c>
       <c r="N60">
-        <v>34.38885393333333</v>
+        <v>34.28291463333333</v>
       </c>
       <c r="O60">
-        <v>8.597213483333332</v>
+        <v>8.570728658333334</v>
       </c>
       <c r="P60">
-        <v>25.79164045</v>
+        <v>25.712185975</v>
       </c>
       <c r="Q60">
-        <v>47.09164045</v>
+        <v>47.012185975</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1433952418783228</v>
+        <v>0.1454832872758051</v>
       </c>
       <c r="T60">
-        <v>1.902312918136692</v>
+        <v>1.943012809410477</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.596707498658605</v>
+        <v>6.484898896986426</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08367589778308009</v>
+        <v>0.0835052939772646</v>
       </c>
       <c r="C61">
-        <v>79.56244930481014</v>
+        <v>77.82262239447303</v>
       </c>
       <c r="D61">
-        <v>163.5714493048102</v>
+        <v>163.782622394473</v>
       </c>
       <c r="E61">
-        <v>-56.191</v>
+        <v>-54.24000000000001</v>
       </c>
       <c r="F61">
-        <v>115.109</v>
+        <v>117.06</v>
       </c>
       <c r="G61">
         <v>31.1</v>
@@ -6283,28 +6283,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M61">
-        <v>6.250418700000001</v>
+        <v>6.356358</v>
       </c>
       <c r="N61">
-        <v>34.28291463333333</v>
+        <v>34.17697533333333</v>
       </c>
       <c r="O61">
-        <v>8.570728658333334</v>
+        <v>8.544243833333333</v>
       </c>
       <c r="P61">
-        <v>25.712185975</v>
+        <v>25.6327315</v>
       </c>
       <c r="Q61">
-        <v>47.012185975</v>
+        <v>46.9327315</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1454832872758051</v>
+        <v>0.1476757349431615</v>
       </c>
       <c r="T61">
-        <v>1.943012809410477</v>
+        <v>1.985747695247951</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.484898896986426</v>
+        <v>6.376817248703319</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0835052939772646</v>
+        <v>0.08333469017144912</v>
       </c>
       <c r="C62">
-        <v>77.82262239447303</v>
+        <v>76.08334144395953</v>
       </c>
       <c r="D62">
-        <v>163.782622394473</v>
+        <v>163.9943414439595</v>
       </c>
       <c r="E62">
-        <v>-54.24000000000001</v>
+        <v>-52.289</v>
       </c>
       <c r="F62">
-        <v>117.06</v>
+        <v>119.011</v>
       </c>
       <c r="G62">
         <v>31.1</v>
@@ -6365,28 +6365,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M62">
-        <v>6.356358</v>
+        <v>6.4622973</v>
       </c>
       <c r="N62">
-        <v>34.17697533333333</v>
+        <v>34.07103603333333</v>
       </c>
       <c r="O62">
-        <v>8.544243833333333</v>
+        <v>8.517759008333332</v>
       </c>
       <c r="P62">
-        <v>25.6327315</v>
+        <v>25.553277025</v>
       </c>
       <c r="Q62">
-        <v>46.9327315</v>
+        <v>46.853277025</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1476757349431615</v>
+        <v>0.1499806158242285</v>
       </c>
       <c r="T62">
-        <v>1.985747695247951</v>
+        <v>2.030674113692475</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.376817248703319</v>
+        <v>6.272279261019658</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08333469017144912</v>
+        <v>0.08316408636563363</v>
       </c>
       <c r="C63">
-        <v>76.08334144395953</v>
+        <v>74.34460857326951</v>
       </c>
       <c r="D63">
-        <v>163.9943414439595</v>
+        <v>164.2066085732695</v>
       </c>
       <c r="E63">
-        <v>-52.289</v>
+        <v>-50.33799999999999</v>
       </c>
       <c r="F63">
-        <v>119.011</v>
+        <v>120.962</v>
       </c>
       <c r="G63">
         <v>31.1</v>
@@ -6447,28 +6447,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M63">
-        <v>6.4622973</v>
+        <v>6.568236600000001</v>
       </c>
       <c r="N63">
-        <v>34.07103603333333</v>
+        <v>33.96509673333333</v>
       </c>
       <c r="O63">
-        <v>8.517759008333332</v>
+        <v>8.491274183333333</v>
       </c>
       <c r="P63">
-        <v>25.553277025</v>
+        <v>25.47382255</v>
       </c>
       <c r="Q63">
-        <v>46.853277025</v>
+        <v>46.77382255000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1499806158242285</v>
+        <v>0.1524068062253517</v>
       </c>
       <c r="T63">
-        <v>2.030674113692475</v>
+        <v>2.077965080476184</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.272279261019658</v>
+        <v>6.171113466487082</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08316408636563363</v>
+        <v>0.08346598255981816</v>
       </c>
       <c r="C64">
-        <v>74.34460857326951</v>
+        <v>72.01835931620531</v>
       </c>
       <c r="D64">
-        <v>164.2066085732695</v>
+        <v>163.8313593162053</v>
       </c>
       <c r="E64">
-        <v>-50.33799999999999</v>
+        <v>-48.387</v>
       </c>
       <c r="F64">
-        <v>120.962</v>
+        <v>122.913</v>
       </c>
       <c r="G64">
         <v>31.1</v>
@@ -6529,45 +6529,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M64">
-        <v>6.568236600000001</v>
+        <v>6.797088900000001</v>
       </c>
       <c r="N64">
-        <v>33.96509673333333</v>
+        <v>33.73624443333333</v>
       </c>
       <c r="O64">
-        <v>8.491274183333333</v>
+        <v>8.434061108333333</v>
       </c>
       <c r="P64">
-        <v>25.47382255</v>
+        <v>25.302183325</v>
       </c>
       <c r="Q64">
-        <v>46.77382255000001</v>
+        <v>46.602183325</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1524068062253517</v>
+        <v>0.1549641420535626</v>
       </c>
       <c r="T64">
-        <v>2.077965080476184</v>
+        <v>2.127812315734688</v>
       </c>
       <c r="U64">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>6.171113466487082</v>
+        <v>5.963337235935421</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08346598255981816</v>
+        <v>0.08330287875400266</v>
       </c>
       <c r="C65">
-        <v>72.01835931620531</v>
+        <v>70.26987992474595</v>
       </c>
       <c r="D65">
-        <v>163.8313593162053</v>
+        <v>164.033879924746</v>
       </c>
       <c r="E65">
-        <v>-48.387</v>
+        <v>-46.43599999999999</v>
       </c>
       <c r="F65">
-        <v>122.913</v>
+        <v>124.864</v>
       </c>
       <c r="G65">
         <v>31.1</v>
@@ -6611,28 +6611,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M65">
-        <v>6.797088900000001</v>
+        <v>6.904979200000001</v>
       </c>
       <c r="N65">
-        <v>33.73624443333333</v>
+        <v>33.62835413333333</v>
       </c>
       <c r="O65">
-        <v>8.434061108333333</v>
+        <v>8.407088533333333</v>
       </c>
       <c r="P65">
-        <v>25.302183325</v>
+        <v>25.2212656</v>
       </c>
       <c r="Q65">
-        <v>46.602183325</v>
+        <v>46.5212656</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1549641420535626</v>
+        <v>0.1576635520944518</v>
       </c>
       <c r="T65">
-        <v>2.127812315734688</v>
+        <v>2.180428841840887</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.963337235935421</v>
+        <v>5.870160091623929</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08330287875400266</v>
+        <v>0.0831397749481872</v>
       </c>
       <c r="C66">
-        <v>70.26987992474595</v>
+        <v>68.52190184585717</v>
       </c>
       <c r="D66">
-        <v>164.033879924746</v>
+        <v>164.2369018458572</v>
       </c>
       <c r="E66">
-        <v>-46.43599999999999</v>
+        <v>-44.48499999999999</v>
       </c>
       <c r="F66">
-        <v>124.864</v>
+        <v>126.815</v>
       </c>
       <c r="G66">
         <v>31.1</v>
@@ -6693,28 +6693,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M66">
-        <v>6.904979200000001</v>
+        <v>7.012869500000002</v>
       </c>
       <c r="N66">
-        <v>33.62835413333333</v>
+        <v>33.52046383333333</v>
       </c>
       <c r="O66">
-        <v>8.407088533333333</v>
+        <v>8.380115958333333</v>
       </c>
       <c r="P66">
-        <v>25.2212656</v>
+        <v>25.140347875</v>
       </c>
       <c r="Q66">
-        <v>46.5212656</v>
+        <v>46.440347875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1576635520944518</v>
+        <v>0.1605172141376777</v>
       </c>
       <c r="T66">
-        <v>2.180428841840887</v>
+        <v>2.236052026581727</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.870160091623929</v>
+        <v>5.779849936368176</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0831397749481872</v>
+        <v>0.08297667114237169</v>
       </c>
       <c r="C67">
-        <v>68.52190184585717</v>
+        <v>66.77442694324375</v>
       </c>
       <c r="D67">
-        <v>164.2369018458572</v>
+        <v>164.4404269432438</v>
       </c>
       <c r="E67">
-        <v>-44.48499999999999</v>
+        <v>-42.53399999999999</v>
       </c>
       <c r="F67">
-        <v>126.815</v>
+        <v>128.766</v>
       </c>
       <c r="G67">
         <v>31.1</v>
@@ -6775,28 +6775,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M67">
-        <v>7.012869500000002</v>
+        <v>7.120759800000001</v>
       </c>
       <c r="N67">
-        <v>33.52046383333333</v>
+        <v>33.41257353333333</v>
       </c>
       <c r="O67">
-        <v>8.380115958333333</v>
+        <v>8.353143383333332</v>
       </c>
       <c r="P67">
-        <v>25.140347875</v>
+        <v>25.05943015</v>
       </c>
       <c r="Q67">
-        <v>46.440347875</v>
+        <v>46.35943014999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1605172141376777</v>
+        <v>0.1635387386540344</v>
       </c>
       <c r="T67">
-        <v>2.236052026581727</v>
+        <v>2.294947163366144</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.779849936368176</v>
+        <v>5.69227645248381</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08297667114237169</v>
+        <v>0.0828135673365562</v>
       </c>
       <c r="C68">
-        <v>66.77442694324375</v>
+        <v>65.02745708985975</v>
       </c>
       <c r="D68">
-        <v>164.4404269432438</v>
+        <v>164.6444570898598</v>
       </c>
       <c r="E68">
-        <v>-42.53399999999999</v>
+        <v>-40.583</v>
       </c>
       <c r="F68">
-        <v>128.766</v>
+        <v>130.717</v>
       </c>
       <c r="G68">
         <v>31.1</v>
@@ -6857,28 +6857,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M68">
-        <v>7.120759800000001</v>
+        <v>7.228650100000001</v>
       </c>
       <c r="N68">
-        <v>33.41257353333333</v>
+        <v>33.30468323333333</v>
       </c>
       <c r="O68">
-        <v>8.353143383333332</v>
+        <v>8.326170808333332</v>
       </c>
       <c r="P68">
-        <v>25.05943015</v>
+        <v>24.978512425</v>
       </c>
       <c r="Q68">
-        <v>46.35943014999999</v>
+        <v>46.278512425</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1635387386540344</v>
+        <v>0.1667433858683522</v>
       </c>
       <c r="T68">
-        <v>2.294947163366144</v>
+        <v>2.35741170237992</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.69227645248381</v>
+        <v>5.607317102446738</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0828135673365562</v>
+        <v>0.08265046353074072</v>
       </c>
       <c r="C69">
-        <v>65.02745708985975</v>
+        <v>63.28099416796641</v>
       </c>
       <c r="D69">
-        <v>164.6444570898598</v>
+        <v>164.8489941679665</v>
       </c>
       <c r="E69">
-        <v>-40.583</v>
+        <v>-38.63199999999998</v>
       </c>
       <c r="F69">
-        <v>130.717</v>
+        <v>132.668</v>
       </c>
       <c r="G69">
         <v>31.1</v>
@@ -6939,28 +6939,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M69">
-        <v>7.228650100000001</v>
+        <v>7.336540400000002</v>
       </c>
       <c r="N69">
-        <v>33.30468323333333</v>
+        <v>33.19679293333333</v>
       </c>
       <c r="O69">
-        <v>8.326170808333332</v>
+        <v>8.299198233333332</v>
       </c>
       <c r="P69">
-        <v>24.978512425</v>
+        <v>24.8975947</v>
       </c>
       <c r="Q69">
-        <v>46.278512425</v>
+        <v>46.1975947</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1667433858683522</v>
+        <v>0.1701483235335648</v>
       </c>
       <c r="T69">
-        <v>2.35741170237992</v>
+        <v>2.423780275082058</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.607317102446738</v>
+        <v>5.52485655682252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08265046353074072</v>
+        <v>0.08248735972492525</v>
       </c>
       <c r="C70">
-        <v>63.28099416796641</v>
+        <v>61.53504006918999</v>
       </c>
       <c r="D70">
-        <v>164.8489941679665</v>
+        <v>165.05404006919</v>
       </c>
       <c r="E70">
-        <v>-38.63199999999998</v>
+        <v>-36.68099999999998</v>
       </c>
       <c r="F70">
-        <v>132.668</v>
+        <v>134.619</v>
       </c>
       <c r="G70">
         <v>31.1</v>
@@ -7021,28 +7021,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M70">
-        <v>7.336540400000002</v>
+        <v>7.444430700000002</v>
       </c>
       <c r="N70">
-        <v>33.19679293333333</v>
+        <v>33.08890263333333</v>
       </c>
       <c r="O70">
-        <v>8.299198233333332</v>
+        <v>8.272225658333333</v>
       </c>
       <c r="P70">
-        <v>24.8975947</v>
+        <v>24.816676975</v>
       </c>
       <c r="Q70">
-        <v>46.1975947</v>
+        <v>46.116676975</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1701483235335648</v>
+        <v>0.1737729345965331</v>
       </c>
       <c r="T70">
-        <v>2.423780275082058</v>
+        <v>2.494430691184333</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.52485655682252</v>
+        <v>5.444786171941036</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08248735972492525</v>
+        <v>0.08232425591910977</v>
       </c>
       <c r="C71">
-        <v>61.53504006918999</v>
+        <v>59.7895966945799</v>
       </c>
       <c r="D71">
-        <v>165.05404006919</v>
+        <v>165.2595966945799</v>
       </c>
       <c r="E71">
-        <v>-36.68099999999998</v>
+        <v>-34.72999999999999</v>
       </c>
       <c r="F71">
-        <v>134.619</v>
+        <v>136.57</v>
       </c>
       <c r="G71">
         <v>31.1</v>
@@ -7103,28 +7103,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M71">
-        <v>7.444430700000002</v>
+        <v>7.552321000000002</v>
       </c>
       <c r="N71">
-        <v>33.08890263333333</v>
+        <v>32.98101233333333</v>
       </c>
       <c r="O71">
-        <v>8.272225658333333</v>
+        <v>8.245253083333333</v>
       </c>
       <c r="P71">
-        <v>24.816676975</v>
+        <v>24.73575925</v>
       </c>
       <c r="Q71">
-        <v>46.116676975</v>
+        <v>46.03575925</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1737729345965331</v>
+        <v>0.1776391863970326</v>
       </c>
       <c r="T71">
-        <v>2.494430691184333</v>
+        <v>2.56979113502676</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.444786171941036</v>
+        <v>5.367003512341878</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08232425591910977</v>
+        <v>0.08216115211329428</v>
       </c>
       <c r="C72">
-        <v>59.7895966945799</v>
+        <v>58.04466595466752</v>
       </c>
       <c r="D72">
-        <v>165.2595966945799</v>
+        <v>165.4656659546676</v>
       </c>
       <c r="E72">
-        <v>-34.72999999999999</v>
+        <v>-32.77899999999997</v>
       </c>
       <c r="F72">
-        <v>136.57</v>
+        <v>138.521</v>
       </c>
       <c r="G72">
         <v>31.1</v>
@@ -7185,28 +7185,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M72">
-        <v>7.552321000000002</v>
+        <v>7.660211300000003</v>
       </c>
       <c r="N72">
-        <v>32.98101233333333</v>
+        <v>32.87312203333333</v>
       </c>
       <c r="O72">
-        <v>8.245253083333333</v>
+        <v>8.218280508333333</v>
       </c>
       <c r="P72">
-        <v>24.73575925</v>
+        <v>24.654841525</v>
       </c>
       <c r="Q72">
-        <v>46.03575925</v>
+        <v>45.954841525</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1776391863970326</v>
+        <v>0.1817720762527389</v>
       </c>
       <c r="T72">
-        <v>2.56979113502676</v>
+        <v>2.65034885085832</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.367003512341878</v>
+        <v>5.291411913576499</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08216115211329429</v>
+        <v>0.0819980483074788</v>
       </c>
       <c r="C73">
-        <v>58.04466595466755</v>
+        <v>56.30024976952555</v>
       </c>
       <c r="D73">
-        <v>165.4656659546676</v>
+        <v>165.6722497695256</v>
       </c>
       <c r="E73">
-        <v>-32.779</v>
+        <v>-30.828</v>
       </c>
       <c r="F73">
-        <v>138.521</v>
+        <v>140.472</v>
       </c>
       <c r="G73">
         <v>31.1</v>
@@ -7267,28 +7267,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M73">
-        <v>7.660211300000001</v>
+        <v>7.7681016</v>
       </c>
       <c r="N73">
-        <v>32.87312203333333</v>
+        <v>32.76523173333333</v>
       </c>
       <c r="O73">
-        <v>8.218280508333333</v>
+        <v>8.191307933333333</v>
       </c>
       <c r="P73">
-        <v>24.654841525</v>
+        <v>24.5739238</v>
       </c>
       <c r="Q73">
-        <v>45.954841525</v>
+        <v>45.8739238</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1817720762527389</v>
+        <v>0.18620017252671</v>
       </c>
       <c r="T73">
-        <v>2.65034885085832</v>
+        <v>2.736660689249276</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.2914119135765</v>
+        <v>5.217920081443493</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0819980483074788</v>
+        <v>0.08183494450166331</v>
       </c>
       <c r="C74">
-        <v>56.30024976952555</v>
+        <v>54.55635006882736</v>
       </c>
       <c r="D74">
-        <v>165.6722497695256</v>
+        <v>165.8793500688274</v>
       </c>
       <c r="E74">
-        <v>-30.828</v>
+        <v>-28.87700000000001</v>
       </c>
       <c r="F74">
-        <v>140.472</v>
+        <v>142.423</v>
       </c>
       <c r="G74">
         <v>31.1</v>
@@ -7349,28 +7349,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M74">
-        <v>7.7681016</v>
+        <v>7.875991900000001</v>
       </c>
       <c r="N74">
-        <v>32.76523173333333</v>
+        <v>32.65734143333333</v>
       </c>
       <c r="O74">
-        <v>8.191307933333333</v>
+        <v>8.164335358333332</v>
       </c>
       <c r="P74">
-        <v>24.5739238</v>
+        <v>24.493006075</v>
       </c>
       <c r="Q74">
-        <v>45.8739238</v>
+        <v>45.79300607499999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.18620017252671</v>
+        <v>0.1909562759320863</v>
       </c>
       <c r="T74">
-        <v>2.736660689249276</v>
+        <v>2.829365997150675</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.217920081443493</v>
+        <v>5.146441724163445</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08183494450166331</v>
+        <v>0.08167184069584782</v>
       </c>
       <c r="C75">
-        <v>54.55635006882736</v>
+        <v>52.81296879190731</v>
       </c>
       <c r="D75">
-        <v>165.8793500688274</v>
+        <v>166.0869687919073</v>
       </c>
       <c r="E75">
-        <v>-28.87700000000001</v>
+        <v>-26.92599999999999</v>
       </c>
       <c r="F75">
-        <v>142.423</v>
+        <v>144.374</v>
       </c>
       <c r="G75">
         <v>31.1</v>
@@ -7431,28 +7431,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M75">
-        <v>7.875991900000001</v>
+        <v>7.983882200000002</v>
       </c>
       <c r="N75">
-        <v>32.65734143333333</v>
+        <v>32.54945113333333</v>
       </c>
       <c r="O75">
-        <v>8.164335358333332</v>
+        <v>8.137362783333332</v>
       </c>
       <c r="P75">
-        <v>24.493006075</v>
+        <v>24.41208835</v>
       </c>
       <c r="Q75">
-        <v>45.79300607499999</v>
+        <v>45.71208835</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1909562759320863</v>
+        <v>0.1960782334455685</v>
       </c>
       <c r="T75">
-        <v>2.829365997150675</v>
+        <v>2.92920248258295</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.146441724163445</v>
+        <v>5.076895214377451</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08167184069584782</v>
+        <v>0.08150873689003234</v>
       </c>
       <c r="C76">
-        <v>52.81296879190731</v>
+        <v>51.07010788782125</v>
       </c>
       <c r="D76">
-        <v>166.0869687919073</v>
+        <v>166.2951078878213</v>
       </c>
       <c r="E76">
-        <v>-26.92599999999999</v>
+        <v>-24.97499999999999</v>
       </c>
       <c r="F76">
-        <v>144.374</v>
+        <v>146.325</v>
       </c>
       <c r="G76">
         <v>31.1</v>
@@ -7513,28 +7513,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M76">
-        <v>7.983882200000002</v>
+        <v>8.091772500000001</v>
       </c>
       <c r="N76">
-        <v>32.54945113333333</v>
+        <v>32.44156083333333</v>
       </c>
       <c r="O76">
-        <v>8.137362783333332</v>
+        <v>8.110390208333332</v>
       </c>
       <c r="P76">
-        <v>24.41208835</v>
+        <v>24.331170625</v>
       </c>
       <c r="Q76">
-        <v>45.71208835</v>
+        <v>45.631170625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1960782334455685</v>
+        <v>0.2016099475601294</v>
       </c>
       <c r="T76">
-        <v>2.92920248258295</v>
+        <v>3.037025886849807</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.076895214377451</v>
+        <v>5.009203278185753</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08150873689003234</v>
+        <v>0.08134563308421686</v>
       </c>
       <c r="C77">
-        <v>51.07010788782125</v>
+        <v>49.32776931540732</v>
       </c>
       <c r="D77">
-        <v>166.2951078878213</v>
+        <v>166.5037693154073</v>
       </c>
       <c r="E77">
-        <v>-24.97499999999999</v>
+        <v>-23.024</v>
       </c>
       <c r="F77">
-        <v>146.325</v>
+        <v>148.276</v>
       </c>
       <c r="G77">
         <v>31.1</v>
@@ -7595,28 +7595,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M77">
-        <v>8.091772500000001</v>
+        <v>8.1996628</v>
       </c>
       <c r="N77">
-        <v>32.44156083333333</v>
+        <v>32.33367053333333</v>
       </c>
       <c r="O77">
-        <v>8.110390208333332</v>
+        <v>8.083417633333333</v>
       </c>
       <c r="P77">
-        <v>24.331170625</v>
+        <v>24.2502529</v>
       </c>
       <c r="Q77">
-        <v>45.631170625</v>
+        <v>45.5502529</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2016099475601294</v>
+        <v>0.2076026378509036</v>
       </c>
       <c r="T77">
-        <v>3.037025886849807</v>
+        <v>3.153834574805569</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.009203278185753</v>
+        <v>4.943292708735941</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08134563308421686</v>
+        <v>0.08118252927840137</v>
       </c>
       <c r="C78">
-        <v>49.32776931540732</v>
+        <v>47.58595504334775</v>
       </c>
       <c r="D78">
-        <v>166.5037693154073</v>
+        <v>166.7129550433478</v>
       </c>
       <c r="E78">
-        <v>-23.024</v>
+        <v>-21.07299999999998</v>
       </c>
       <c r="F78">
-        <v>148.276</v>
+        <v>150.227</v>
       </c>
       <c r="G78">
         <v>31.1</v>
@@ -7677,28 +7677,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M78">
-        <v>8.1996628</v>
+        <v>8.307553100000002</v>
       </c>
       <c r="N78">
-        <v>32.33367053333333</v>
+        <v>32.22578023333333</v>
       </c>
       <c r="O78">
-        <v>8.083417633333333</v>
+        <v>8.056445058333333</v>
       </c>
       <c r="P78">
-        <v>24.2502529</v>
+        <v>24.169335175</v>
       </c>
       <c r="Q78">
-        <v>45.5502529</v>
+        <v>45.469335175</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2076026378509036</v>
+        <v>0.2141164316452234</v>
       </c>
       <c r="T78">
-        <v>3.153834574805569</v>
+        <v>3.280800539974876</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.943292708735941</v>
+        <v>4.87909410212898</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08118252927840137</v>
+        <v>0.08101942547258588</v>
       </c>
       <c r="C79">
-        <v>47.58595504334775</v>
+        <v>45.84466705023038</v>
       </c>
       <c r="D79">
-        <v>166.7129550433478</v>
+        <v>166.9226670502304</v>
       </c>
       <c r="E79">
-        <v>-21.07299999999998</v>
+        <v>-19.12199999999999</v>
       </c>
       <c r="F79">
-        <v>150.227</v>
+        <v>152.178</v>
       </c>
       <c r="G79">
         <v>31.1</v>
@@ -7759,28 +7759,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M79">
-        <v>8.307553100000002</v>
+        <v>8.415443400000001</v>
       </c>
       <c r="N79">
-        <v>32.22578023333333</v>
+        <v>32.11788993333333</v>
       </c>
       <c r="O79">
-        <v>8.056445058333333</v>
+        <v>8.029472483333333</v>
       </c>
       <c r="P79">
-        <v>24.169335175</v>
+        <v>24.08841745</v>
       </c>
       <c r="Q79">
-        <v>45.469335175</v>
+        <v>45.38841745</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2141164316452234</v>
+        <v>0.221222388511754</v>
       </c>
       <c r="T79">
-        <v>3.280800539974876</v>
+        <v>3.419308865614119</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.87909410212898</v>
+        <v>4.816541613640148</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08101942547258588</v>
+        <v>0.0808563216667704</v>
       </c>
       <c r="C80">
-        <v>45.84466705023038</v>
+        <v>44.10390732461136</v>
       </c>
       <c r="D80">
-        <v>166.9226670502304</v>
+        <v>167.1329073246114</v>
       </c>
       <c r="E80">
-        <v>-19.12199999999999</v>
+        <v>-17.17099999999999</v>
       </c>
       <c r="F80">
-        <v>152.178</v>
+        <v>154.129</v>
       </c>
       <c r="G80">
         <v>31.1</v>
@@ -7841,28 +7841,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M80">
-        <v>8.415443400000001</v>
+        <v>8.523333700000002</v>
       </c>
       <c r="N80">
-        <v>32.11788993333333</v>
+        <v>32.00999963333333</v>
       </c>
       <c r="O80">
-        <v>8.029472483333333</v>
+        <v>8.002499908333332</v>
       </c>
       <c r="P80">
-        <v>24.08841745</v>
+        <v>24.007499725</v>
       </c>
       <c r="Q80">
-        <v>45.38841745</v>
+        <v>45.307499725</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.221222388511754</v>
+        <v>0.2290051031750972</v>
       </c>
       <c r="T80">
-        <v>3.419308865614119</v>
+        <v>3.571008460361861</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.816541613640148</v>
+        <v>4.755572732454828</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0808563216667704</v>
+        <v>0.08069321786095493</v>
       </c>
       <c r="C81">
-        <v>44.10390732461136</v>
+        <v>42.36367786507773</v>
       </c>
       <c r="D81">
-        <v>167.1329073246114</v>
+        <v>167.3436778650778</v>
       </c>
       <c r="E81">
-        <v>-17.17099999999999</v>
+        <v>-15.21999999999997</v>
       </c>
       <c r="F81">
-        <v>154.129</v>
+        <v>156.08</v>
       </c>
       <c r="G81">
         <v>31.1</v>
@@ -7923,28 +7923,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M81">
-        <v>8.523333700000002</v>
+        <v>8.631224000000003</v>
       </c>
       <c r="N81">
-        <v>32.00999963333333</v>
+        <v>31.90210933333333</v>
       </c>
       <c r="O81">
-        <v>8.002499908333332</v>
+        <v>7.975527333333332</v>
       </c>
       <c r="P81">
-        <v>24.007499725</v>
+        <v>23.926582</v>
       </c>
       <c r="Q81">
-        <v>45.307499725</v>
+        <v>45.22658199999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2290051031750972</v>
+        <v>0.2375660893047747</v>
       </c>
       <c r="T81">
-        <v>3.571008460361861</v>
+        <v>3.737878014584379</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.755572732454828</v>
+        <v>4.696128073299143</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08069321786095493</v>
+        <v>0.08053011405513943</v>
       </c>
       <c r="C82">
-        <v>42.36367786507773</v>
+        <v>40.62398068031112</v>
       </c>
       <c r="D82">
-        <v>167.3436778650778</v>
+        <v>167.5549806803112</v>
       </c>
       <c r="E82">
-        <v>-15.21999999999997</v>
+        <v>-13.26899999999998</v>
       </c>
       <c r="F82">
-        <v>156.08</v>
+        <v>158.031</v>
       </c>
       <c r="G82">
         <v>31.1</v>
@@ -8005,28 +8005,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M82">
-        <v>8.631224000000003</v>
+        <v>8.739114300000002</v>
       </c>
       <c r="N82">
-        <v>31.90210933333333</v>
+        <v>31.79421903333333</v>
       </c>
       <c r="O82">
-        <v>7.975527333333332</v>
+        <v>7.948554758333332</v>
       </c>
       <c r="P82">
-        <v>23.926582</v>
+        <v>23.845664275</v>
       </c>
       <c r="Q82">
-        <v>45.22658199999999</v>
+        <v>45.145664275</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2375660893047747</v>
+        <v>0.247028231869155</v>
       </c>
       <c r="T82">
-        <v>3.737878014584379</v>
+        <v>3.922312785040845</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.696128073299143</v>
+        <v>4.638151183505326</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08053011405513943</v>
+        <v>0.08036701024932394</v>
       </c>
       <c r="C83">
-        <v>40.62398068031112</v>
+        <v>38.88481778915119</v>
       </c>
       <c r="D83">
-        <v>167.5549806803112</v>
+        <v>167.7668177891512</v>
       </c>
       <c r="E83">
-        <v>-13.26899999999998</v>
+        <v>-11.31799999999998</v>
       </c>
       <c r="F83">
-        <v>158.031</v>
+        <v>159.982</v>
       </c>
       <c r="G83">
         <v>31.1</v>
@@ -8087,28 +8087,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M83">
-        <v>8.739114300000002</v>
+        <v>8.847004600000002</v>
       </c>
       <c r="N83">
-        <v>31.79421903333333</v>
+        <v>31.68632873333333</v>
       </c>
       <c r="O83">
-        <v>7.948554758333332</v>
+        <v>7.921582183333332</v>
       </c>
       <c r="P83">
-        <v>23.845664275</v>
+        <v>23.76474655</v>
       </c>
       <c r="Q83">
-        <v>45.145664275</v>
+        <v>45.06474655</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.247028231869155</v>
+        <v>0.2575417236073553</v>
       </c>
       <c r="T83">
-        <v>3.922312785040845</v>
+        <v>4.127240307770252</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.638151183505326</v>
+        <v>4.581588364194285</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08036701024932394</v>
+        <v>0.08020390644350847</v>
       </c>
       <c r="C84">
-        <v>38.88481778915119</v>
+        <v>37.14619122065994</v>
       </c>
       <c r="D84">
-        <v>167.7668177891512</v>
+        <v>167.97919122066</v>
       </c>
       <c r="E84">
-        <v>-11.31799999999998</v>
+        <v>-9.36699999999999</v>
       </c>
       <c r="F84">
-        <v>159.982</v>
+        <v>161.933</v>
       </c>
       <c r="G84">
         <v>31.1</v>
@@ -8169,28 +8169,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M84">
-        <v>8.847004600000002</v>
+        <v>8.954894900000001</v>
       </c>
       <c r="N84">
-        <v>31.68632873333333</v>
+        <v>31.57843843333333</v>
       </c>
       <c r="O84">
-        <v>7.921582183333332</v>
+        <v>7.894609608333333</v>
       </c>
       <c r="P84">
-        <v>23.76474655</v>
+        <v>23.683828825</v>
       </c>
       <c r="Q84">
-        <v>45.06474655</v>
+        <v>44.983828825</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2575417236073553</v>
+        <v>0.2692920967265205</v>
       </c>
       <c r="T84">
-        <v>4.127240307770252</v>
+        <v>4.356276950820766</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.581588364194285</v>
+        <v>4.526388504384717</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08020390644350847</v>
+        <v>0.08161580263769297</v>
       </c>
       <c r="C85">
-        <v>37.14619122065994</v>
+        <v>33.37442097949176</v>
       </c>
       <c r="D85">
-        <v>167.97919122066</v>
+        <v>166.1584209794918</v>
       </c>
       <c r="E85">
-        <v>-9.36699999999999</v>
+        <v>-7.415999999999968</v>
       </c>
       <c r="F85">
-        <v>161.933</v>
+        <v>163.884</v>
       </c>
       <c r="G85">
         <v>31.1</v>
@@ -8251,45 +8251,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M85">
-        <v>8.954894900000001</v>
+        <v>9.472495200000003</v>
       </c>
       <c r="N85">
-        <v>31.57843843333333</v>
+        <v>31.06083813333333</v>
       </c>
       <c r="O85">
-        <v>7.894609608333333</v>
+        <v>7.765209533333332</v>
       </c>
       <c r="P85">
-        <v>23.683828825</v>
+        <v>23.29562859999999</v>
       </c>
       <c r="Q85">
-        <v>44.983828825</v>
+        <v>44.5956286</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2692920967265205</v>
+        <v>0.2825112664855812</v>
       </c>
       <c r="T85">
-        <v>4.356276950820766</v>
+        <v>4.613943174252594</v>
       </c>
       <c r="U85">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>4.526388504384717</v>
+        <v>4.279055568519404</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08161580263769298</v>
+        <v>0.08147144883187751</v>
       </c>
       <c r="C86">
-        <v>33.37442097949176</v>
+        <v>31.60776499681907</v>
       </c>
       <c r="D86">
-        <v>166.1584209794918</v>
+        <v>166.3427649968191</v>
       </c>
       <c r="E86">
-        <v>-7.415999999999997</v>
+        <v>-5.465000000000003</v>
       </c>
       <c r="F86">
-        <v>163.884</v>
+        <v>165.835</v>
       </c>
       <c r="G86">
         <v>31.1</v>
@@ -8333,28 +8333,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M86">
-        <v>9.472495200000001</v>
+        <v>9.585263000000001</v>
       </c>
       <c r="N86">
-        <v>31.06083813333333</v>
+        <v>30.94807033333333</v>
       </c>
       <c r="O86">
-        <v>7.765209533333333</v>
+        <v>7.737017583333333</v>
       </c>
       <c r="P86">
-        <v>23.2956286</v>
+        <v>23.21105275</v>
       </c>
       <c r="Q86">
-        <v>44.5956286</v>
+        <v>44.51105275</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2825112664855811</v>
+        <v>0.2974929922125167</v>
       </c>
       <c r="T86">
-        <v>4.613943174252591</v>
+        <v>4.905964894141996</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.279055568519404</v>
+        <v>4.228713738301529</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08147144883187751</v>
+        <v>0.08132709502606203</v>
       </c>
       <c r="C87">
-        <v>31.60776499681907</v>
+        <v>29.84151850841613</v>
       </c>
       <c r="D87">
-        <v>166.3427649968191</v>
+        <v>166.5275185084162</v>
       </c>
       <c r="E87">
-        <v>-5.465000000000003</v>
+        <v>-3.513999999999982</v>
       </c>
       <c r="F87">
-        <v>165.835</v>
+        <v>167.786</v>
       </c>
       <c r="G87">
         <v>31.1</v>
@@ -8415,28 +8415,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M87">
-        <v>9.585263000000001</v>
+        <v>9.698030800000003</v>
       </c>
       <c r="N87">
-        <v>30.94807033333333</v>
+        <v>30.83530253333333</v>
       </c>
       <c r="O87">
-        <v>7.737017583333333</v>
+        <v>7.708825633333332</v>
       </c>
       <c r="P87">
-        <v>23.21105275</v>
+        <v>23.12647689999999</v>
       </c>
       <c r="Q87">
-        <v>44.51105275</v>
+        <v>44.4264769</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2974929922125167</v>
+        <v>0.3146149644718715</v>
       </c>
       <c r="T87">
-        <v>4.905964894141996</v>
+        <v>5.23970400258703</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.228713738301529</v>
+        <v>4.179542648321277</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08132709502606203</v>
+        <v>0.08118274122024652</v>
       </c>
       <c r="C88">
-        <v>29.84151850841613</v>
+        <v>28.07568288025098</v>
       </c>
       <c r="D88">
-        <v>166.5275185084162</v>
+        <v>166.712682880251</v>
       </c>
       <c r="E88">
-        <v>-3.513999999999982</v>
+        <v>-1.562999999999988</v>
       </c>
       <c r="F88">
-        <v>167.786</v>
+        <v>169.737</v>
       </c>
       <c r="G88">
         <v>31.1</v>
@@ -8497,28 +8497,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M88">
-        <v>9.698030800000003</v>
+        <v>9.810798600000002</v>
       </c>
       <c r="N88">
-        <v>30.83530253333333</v>
+        <v>30.72253473333333</v>
       </c>
       <c r="O88">
-        <v>7.708825633333332</v>
+        <v>7.680633683333332</v>
       </c>
       <c r="P88">
-        <v>23.12647689999999</v>
+        <v>23.04190105</v>
       </c>
       <c r="Q88">
-        <v>44.4264769</v>
+        <v>44.34190105</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3146149644718715</v>
+        <v>0.3343710863095887</v>
       </c>
       <c r="T88">
-        <v>5.23970400258703</v>
+        <v>5.624787589254375</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.179542648321277</v>
+        <v>4.131501928225632</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08118274122024652</v>
+        <v>0.08103838741443105</v>
       </c>
       <c r="C89">
-        <v>28.07568288025098</v>
+        <v>26.31025948437349</v>
       </c>
       <c r="D89">
-        <v>166.712682880251</v>
+        <v>166.8982594843735</v>
       </c>
       <c r="E89">
-        <v>-1.562999999999988</v>
+        <v>0.3880000000000052</v>
       </c>
       <c r="F89">
-        <v>169.737</v>
+        <v>171.688</v>
       </c>
       <c r="G89">
         <v>31.1</v>
@@ -8579,28 +8579,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M89">
-        <v>9.810798600000002</v>
+        <v>9.923566400000002</v>
       </c>
       <c r="N89">
-        <v>30.72253473333333</v>
+        <v>30.60976693333333</v>
       </c>
       <c r="O89">
-        <v>7.680633683333332</v>
+        <v>7.652441733333332</v>
       </c>
       <c r="P89">
-        <v>23.04190105</v>
+        <v>22.9573252</v>
       </c>
       <c r="Q89">
-        <v>44.34190105</v>
+        <v>44.2573252</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3343710863095887</v>
+        <v>0.3574198951202587</v>
       </c>
       <c r="T89">
-        <v>5.624787589254375</v>
+        <v>6.074051773699614</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.131501928225632</v>
+        <v>4.084553042677612</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08103838741443105</v>
+        <v>0.08089403360861555</v>
       </c>
       <c r="C90">
-        <v>26.31025948437349</v>
+        <v>24.54524969894987</v>
       </c>
       <c r="D90">
-        <v>166.8982594843735</v>
+        <v>167.0842496989499</v>
       </c>
       <c r="E90">
-        <v>0.3880000000000052</v>
+        <v>2.338999999999999</v>
       </c>
       <c r="F90">
-        <v>171.688</v>
+        <v>173.639</v>
       </c>
       <c r="G90">
         <v>31.1</v>
@@ -8661,28 +8661,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M90">
-        <v>9.923566400000002</v>
+        <v>10.0363342</v>
       </c>
       <c r="N90">
-        <v>30.60976693333333</v>
+        <v>30.49699913333333</v>
       </c>
       <c r="O90">
-        <v>7.652441733333332</v>
+        <v>7.624249783333333</v>
       </c>
       <c r="P90">
-        <v>22.9573252</v>
+        <v>22.87274935</v>
       </c>
       <c r="Q90">
-        <v>44.2573252</v>
+        <v>44.17274935</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3574198951202587</v>
+        <v>0.3846593964419597</v>
       </c>
       <c r="T90">
-        <v>6.074051773699614</v>
+        <v>6.605000355316713</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.084553042677612</v>
+        <v>4.038659188265505</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08089403360861555</v>
+        <v>0.08311217980280008</v>
       </c>
       <c r="C91">
-        <v>24.54524969894987</v>
+        <v>19.78130035831603</v>
       </c>
       <c r="D91">
-        <v>167.0842496989499</v>
+        <v>164.2713003583161</v>
       </c>
       <c r="E91">
-        <v>2.338999999999999</v>
+        <v>4.29000000000002</v>
       </c>
       <c r="F91">
-        <v>173.639</v>
+        <v>175.59</v>
       </c>
       <c r="G91">
         <v>31.1</v>
@@ -8743,45 +8743,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M91">
-        <v>10.0363342</v>
+        <v>10.763667</v>
       </c>
       <c r="N91">
-        <v>30.49699913333333</v>
+        <v>29.76966633333333</v>
       </c>
       <c r="O91">
-        <v>7.624249783333333</v>
+        <v>7.442416583333332</v>
       </c>
       <c r="P91">
-        <v>22.87274935</v>
+        <v>22.32724975</v>
       </c>
       <c r="Q91">
-        <v>44.17274935</v>
+        <v>43.62724975</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3846593964419597</v>
+        <v>0.4173467980280009</v>
       </c>
       <c r="T91">
-        <v>6.605000355316713</v>
+        <v>7.242138653257234</v>
       </c>
       <c r="U91">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.038659188265505</v>
+        <v>3.76575504735824</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08311217980280008</v>
+        <v>0.08299407599698461</v>
       </c>
       <c r="C92">
-        <v>19.78130035831603</v>
+        <v>17.97768468238991</v>
       </c>
       <c r="D92">
-        <v>164.2713003583161</v>
+        <v>164.4186846823899</v>
       </c>
       <c r="E92">
-        <v>4.29000000000002</v>
+        <v>6.241000000000014</v>
       </c>
       <c r="F92">
-        <v>175.59</v>
+        <v>177.541</v>
       </c>
       <c r="G92">
         <v>31.1</v>
@@ -8825,28 +8825,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M92">
-        <v>10.763667</v>
+        <v>10.8832633</v>
       </c>
       <c r="N92">
-        <v>29.76966633333333</v>
+        <v>29.65007003333333</v>
       </c>
       <c r="O92">
-        <v>7.442416583333332</v>
+        <v>7.412517508333332</v>
       </c>
       <c r="P92">
-        <v>22.32724975</v>
+        <v>22.237552525</v>
       </c>
       <c r="Q92">
-        <v>43.62724975</v>
+        <v>43.537552525</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4173467980280009</v>
+        <v>0.4572980666331623</v>
       </c>
       <c r="T92">
-        <v>7.242138653257234</v>
+        <v>8.02086323962898</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.76575504735824</v>
+        <v>3.724373123760897</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08299407599698461</v>
+        <v>0.0828759721911691</v>
       </c>
       <c r="C93">
-        <v>17.97768468238991</v>
+        <v>16.17433371059104</v>
       </c>
       <c r="D93">
-        <v>164.4186846823899</v>
+        <v>164.5663337105911</v>
       </c>
       <c r="E93">
-        <v>6.241000000000014</v>
+        <v>8.192000000000007</v>
       </c>
       <c r="F93">
-        <v>177.541</v>
+        <v>179.492</v>
       </c>
       <c r="G93">
         <v>31.1</v>
@@ -8907,28 +8907,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M93">
-        <v>10.8832633</v>
+        <v>11.0028596</v>
       </c>
       <c r="N93">
-        <v>29.65007003333333</v>
+        <v>29.53047373333333</v>
       </c>
       <c r="O93">
-        <v>7.412517508333332</v>
+        <v>7.382618433333333</v>
       </c>
       <c r="P93">
-        <v>22.237552525</v>
+        <v>22.1478553</v>
       </c>
       <c r="Q93">
-        <v>43.537552525</v>
+        <v>43.4478553</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4572980666331623</v>
+        <v>0.5072371523896141</v>
       </c>
       <c r="T93">
-        <v>8.02086323962898</v>
+        <v>8.994268972593664</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.724373123760897</v>
+        <v>3.683890807198279</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0828759721911691</v>
+        <v>0.08275786838535362</v>
       </c>
       <c r="C94">
-        <v>16.17433371059104</v>
+        <v>14.37124815667843</v>
       </c>
       <c r="D94">
-        <v>164.5663337105911</v>
+        <v>164.7142481566785</v>
       </c>
       <c r="E94">
-        <v>8.192000000000007</v>
+        <v>10.14300000000003</v>
       </c>
       <c r="F94">
-        <v>179.492</v>
+        <v>181.443</v>
       </c>
       <c r="G94">
         <v>31.1</v>
@@ -8989,28 +8989,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M94">
-        <v>11.0028596</v>
+        <v>11.1224559</v>
       </c>
       <c r="N94">
-        <v>29.53047373333333</v>
+        <v>29.41087743333333</v>
       </c>
       <c r="O94">
-        <v>7.382618433333333</v>
+        <v>7.352719358333332</v>
       </c>
       <c r="P94">
-        <v>22.1478553</v>
+        <v>22.058158075</v>
       </c>
       <c r="Q94">
-        <v>43.4478553</v>
+        <v>43.358158075</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5072371523896141</v>
+        <v>0.571444548362195</v>
       </c>
       <c r="T94">
-        <v>8.994268972593664</v>
+        <v>10.24579062926254</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.683890807198279</v>
+        <v>3.644279078088619</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08275786838535362</v>
+        <v>0.08263976457953814</v>
       </c>
       <c r="C95">
-        <v>14.37124815667843</v>
+        <v>12.56842873697951</v>
       </c>
       <c r="D95">
-        <v>164.7142481566785</v>
+        <v>164.8624287369796</v>
       </c>
       <c r="E95">
-        <v>10.14300000000003</v>
+        <v>12.09400000000002</v>
       </c>
       <c r="F95">
-        <v>181.443</v>
+        <v>183.394</v>
       </c>
       <c r="G95">
         <v>31.1</v>
@@ -9071,28 +9071,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M95">
-        <v>11.1224559</v>
+        <v>11.2420522</v>
       </c>
       <c r="N95">
-        <v>29.41087743333333</v>
+        <v>29.29128113333333</v>
       </c>
       <c r="O95">
-        <v>7.352719358333332</v>
+        <v>7.322820283333332</v>
       </c>
       <c r="P95">
-        <v>22.058158075</v>
+        <v>21.96846085</v>
       </c>
       <c r="Q95">
-        <v>43.358158075</v>
+        <v>43.26846085</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.571444548362195</v>
+        <v>0.6570544096589696</v>
       </c>
       <c r="T95">
-        <v>10.24579062926254</v>
+        <v>11.91448617148771</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.644279078088619</v>
+        <v>3.605510151725974</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08263976457953814</v>
+        <v>0.08252166077372267</v>
       </c>
       <c r="C96">
-        <v>12.56842873697951</v>
+        <v>10.76587617040164</v>
       </c>
       <c r="D96">
-        <v>164.8624287369796</v>
+        <v>165.0108761704017</v>
       </c>
       <c r="E96">
-        <v>12.09400000000002</v>
+        <v>14.04500000000002</v>
       </c>
       <c r="F96">
-        <v>183.394</v>
+        <v>185.345</v>
       </c>
       <c r="G96">
         <v>31.1</v>
@@ -9153,28 +9153,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M96">
-        <v>11.2420522</v>
+        <v>11.3616485</v>
       </c>
       <c r="N96">
-        <v>29.29128113333333</v>
+        <v>29.17168483333333</v>
       </c>
       <c r="O96">
-        <v>7.322820283333332</v>
+        <v>7.292921208333333</v>
       </c>
       <c r="P96">
-        <v>21.96846085</v>
+        <v>21.878763625</v>
       </c>
       <c r="Q96">
-        <v>43.26846085</v>
+        <v>43.178763625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6570544096589696</v>
+        <v>0.7769082154744541</v>
       </c>
       <c r="T96">
-        <v>11.91448617148771</v>
+        <v>14.25065993060296</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.605510151725974</v>
+        <v>3.567557413286754</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08252166077372267</v>
+        <v>0.08240355696790719</v>
       </c>
       <c r="C97">
-        <v>10.76587617040164</v>
+        <v>8.96359117844392</v>
       </c>
       <c r="D97">
-        <v>165.0108761704017</v>
+        <v>165.159591178444</v>
       </c>
       <c r="E97">
-        <v>14.04500000000002</v>
+        <v>15.99600000000004</v>
       </c>
       <c r="F97">
-        <v>185.345</v>
+        <v>187.296</v>
       </c>
       <c r="G97">
         <v>31.1</v>
@@ -9235,28 +9235,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M97">
-        <v>11.3616485</v>
+        <v>11.4812448</v>
       </c>
       <c r="N97">
-        <v>29.17168483333333</v>
+        <v>29.05208853333333</v>
       </c>
       <c r="O97">
-        <v>7.292921208333333</v>
+        <v>7.263022133333332</v>
       </c>
       <c r="P97">
-        <v>21.878763625</v>
+        <v>21.7890664</v>
       </c>
       <c r="Q97">
-        <v>43.178763625</v>
+        <v>43.08906639999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7769082154744541</v>
+        <v>0.956688924197681</v>
       </c>
       <c r="T97">
-        <v>14.25065993060296</v>
+        <v>17.75492056927583</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.567557413286754</v>
+        <v>3.53039535689835</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08240355696790719</v>
+        <v>0.08432245316209169</v>
       </c>
       <c r="C98">
-        <v>8.963591178443949</v>
+        <v>4.629062637531888</v>
       </c>
       <c r="D98">
-        <v>165.159591178444</v>
+        <v>162.7760626375319</v>
       </c>
       <c r="E98">
-        <v>15.99600000000001</v>
+        <v>17.947</v>
       </c>
       <c r="F98">
-        <v>187.296</v>
+        <v>189.247</v>
       </c>
       <c r="G98">
         <v>31.1</v>
@@ -9317,45 +9317,45 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M98">
-        <v>11.4812448</v>
+        <v>12.1307327</v>
       </c>
       <c r="N98">
-        <v>29.05208853333333</v>
+        <v>28.40260063333333</v>
       </c>
       <c r="O98">
-        <v>7.263022133333333</v>
+        <v>7.100650158333332</v>
       </c>
       <c r="P98">
-        <v>21.7890664</v>
+        <v>21.301950475</v>
       </c>
       <c r="Q98">
-        <v>43.0890664</v>
+        <v>42.601950475</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9566889241976786</v>
+        <v>1.256323438736389</v>
       </c>
       <c r="T98">
-        <v>17.75492056927578</v>
+        <v>23.59535496706387</v>
       </c>
       <c r="U98">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.53039535689835</v>
+        <v>3.34137552411268</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08432245316209169</v>
+        <v>0.08422534935627622</v>
       </c>
       <c r="C99">
-        <v>4.629062637531888</v>
+        <v>2.797024881588385</v>
       </c>
       <c r="D99">
-        <v>162.7760626375319</v>
+        <v>162.8950248815884</v>
       </c>
       <c r="E99">
-        <v>17.947</v>
+        <v>19.898</v>
       </c>
       <c r="F99">
-        <v>189.247</v>
+        <v>191.198</v>
       </c>
       <c r="G99">
         <v>31.1</v>
@@ -9399,28 +9399,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M99">
-        <v>12.1307327</v>
+        <v>12.2557918</v>
       </c>
       <c r="N99">
-        <v>28.40260063333333</v>
+        <v>28.27754153333333</v>
       </c>
       <c r="O99">
-        <v>7.100650158333332</v>
+        <v>7.069385383333333</v>
       </c>
       <c r="P99">
-        <v>21.301950475</v>
+        <v>21.20815615</v>
       </c>
       <c r="Q99">
-        <v>42.601950475</v>
+        <v>42.50815615</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.256323438736389</v>
+        <v>1.855592467813809</v>
       </c>
       <c r="T99">
-        <v>23.59535496706387</v>
+        <v>35.27622376264004</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.34137552411268</v>
+        <v>3.307279855499285</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08422534935627622</v>
+        <v>0.08412824555046072</v>
       </c>
       <c r="C100">
-        <v>2.797024881588385</v>
+        <v>0.9651611360689571</v>
       </c>
       <c r="D100">
-        <v>162.8950248815884</v>
+        <v>163.014161136069</v>
       </c>
       <c r="E100">
-        <v>19.898</v>
+        <v>21.84900000000002</v>
       </c>
       <c r="F100">
-        <v>191.198</v>
+        <v>193.149</v>
       </c>
       <c r="G100">
         <v>31.1</v>
@@ -9481,28 +9481,28 @@
         <v>40.53333333333333</v>
       </c>
       <c r="M100">
-        <v>12.2557918</v>
+        <v>12.3808509</v>
       </c>
       <c r="N100">
-        <v>28.27754153333333</v>
+        <v>28.15248243333333</v>
       </c>
       <c r="O100">
-        <v>7.069385383333333</v>
+        <v>7.038120608333332</v>
       </c>
       <c r="P100">
-        <v>21.20815615</v>
+        <v>21.114361825</v>
       </c>
       <c r="Q100">
-        <v>42.50815615</v>
+        <v>42.414361825</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.855592467813809</v>
+        <v>3.653399555046069</v>
       </c>
       <c r="T100">
-        <v>35.27622376264004</v>
+        <v>70.31883014936855</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.307279855499285</v>
+        <v>3.27387298827202</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08412824555046072</v>
-      </c>
-      <c r="C101">
-        <v>0.9651611360689571</v>
-      </c>
-      <c r="D101">
-        <v>163.014161136069</v>
-      </c>
-      <c r="E101">
-        <v>21.84900000000002</v>
-      </c>
-      <c r="F101">
-        <v>193.149</v>
-      </c>
-      <c r="G101">
-        <v>31.1</v>
-      </c>
-      <c r="H101">
-        <v>23.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>61.83333333333334</v>
-      </c>
-      <c r="K101">
-        <v>21.3</v>
-      </c>
-      <c r="L101">
-        <v>40.53333333333333</v>
-      </c>
-      <c r="M101">
-        <v>12.3808509</v>
-      </c>
-      <c r="N101">
-        <v>28.15248243333333</v>
-      </c>
-      <c r="O101">
-        <v>7.038120608333332</v>
-      </c>
-      <c r="P101">
-        <v>21.114361825</v>
-      </c>
-      <c r="Q101">
-        <v>42.414361825</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.653399555046069</v>
-      </c>
-      <c r="T101">
-        <v>70.31883014936855</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.04807500000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.27387298827202</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
